--- a/output/Hubei/黄石市_news.xlsx
+++ b/output/Hubei/黄石市_news.xlsx
@@ -4098,7 +4098,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4109,13 +4109,6 @@
     <font>
       <b/>
       <sz val="11"/>
-      <name val="宋体"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -4583,28 +4576,31 @@
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="43" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="2" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -4613,126 +4609,124 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="4" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="9" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="6"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -5172,9 +5166,7 @@
       <c r="M2">
         <v>105</v>
       </c>
-      <c r="N2">
-        <v>0</v>
-      </c>
+      <c r="N2"/>
       <c r="O2" t="s">
         <v>24</v>
       </c>
@@ -5222,9 +5214,7 @@
       <c r="M3">
         <v>54</v>
       </c>
-      <c r="N3">
-        <v>0</v>
-      </c>
+      <c r="N3"/>
       <c r="O3" t="s">
         <v>31</v>
       </c>
@@ -5272,9 +5262,7 @@
       <c r="M4">
         <v>15</v>
       </c>
-      <c r="N4">
-        <v>0</v>
-      </c>
+      <c r="N4"/>
       <c r="O4" t="s">
         <v>33</v>
       </c>
@@ -5322,9 +5310,7 @@
       <c r="M5">
         <v>25</v>
       </c>
-      <c r="N5">
-        <v>0</v>
-      </c>
+      <c r="N5"/>
       <c r="O5" t="s">
         <v>38</v>
       </c>
@@ -5372,10 +5358,8 @@
       <c r="M6">
         <v>27</v>
       </c>
-      <c r="N6">
-        <v>0</v>
-      </c>
-      <c r="O6" t="s">
+      <c r="N6"/>
+      <c r="O6" s="2" t="s">
         <v>40</v>
       </c>
       <c r="P6" t="s">
@@ -5422,9 +5406,7 @@
       <c r="M7">
         <v>19</v>
       </c>
-      <c r="N7">
-        <v>0</v>
-      </c>
+      <c r="N7"/>
       <c r="O7" t="s">
         <v>42</v>
       </c>
@@ -5472,9 +5454,7 @@
       <c r="M8">
         <v>20</v>
       </c>
-      <c r="N8">
-        <v>0</v>
-      </c>
+      <c r="N8"/>
       <c r="O8" t="s">
         <v>44</v>
       </c>
@@ -5522,9 +5502,7 @@
       <c r="M9">
         <v>19</v>
       </c>
-      <c r="N9">
-        <v>0</v>
-      </c>
+      <c r="N9"/>
       <c r="O9" t="s">
         <v>47</v>
       </c>
@@ -5572,9 +5550,7 @@
       <c r="M10">
         <v>17</v>
       </c>
-      <c r="N10">
-        <v>0</v>
-      </c>
+      <c r="N10"/>
       <c r="O10" t="s">
         <v>49</v>
       </c>
@@ -5622,9 +5598,7 @@
       <c r="M11">
         <v>17</v>
       </c>
-      <c r="N11">
-        <v>0</v>
-      </c>
+      <c r="N11"/>
       <c r="O11" t="s">
         <v>51</v>
       </c>
@@ -5672,9 +5646,7 @@
       <c r="M12">
         <v>17</v>
       </c>
-      <c r="N12">
-        <v>0</v>
-      </c>
+      <c r="N12"/>
       <c r="O12" t="s">
         <v>53</v>
       </c>
@@ -5722,9 +5694,7 @@
       <c r="M13">
         <v>51</v>
       </c>
-      <c r="N13">
-        <v>0</v>
-      </c>
+      <c r="N13"/>
       <c r="O13" t="s">
         <v>58</v>
       </c>
@@ -5772,9 +5742,7 @@
       <c r="M14">
         <v>19</v>
       </c>
-      <c r="N14">
-        <v>0</v>
-      </c>
+      <c r="N14"/>
       <c r="O14" t="s">
         <v>61</v>
       </c>
@@ -5822,9 +5790,7 @@
       <c r="M15">
         <v>16</v>
       </c>
-      <c r="N15">
-        <v>0</v>
-      </c>
+      <c r="N15"/>
       <c r="O15" t="s">
         <v>63</v>
       </c>
@@ -5872,9 +5838,7 @@
       <c r="M16">
         <v>16</v>
       </c>
-      <c r="N16">
-        <v>0</v>
-      </c>
+      <c r="N16"/>
       <c r="O16" t="s">
         <v>65</v>
       </c>
@@ -5922,9 +5886,7 @@
       <c r="M17">
         <v>14</v>
       </c>
-      <c r="N17">
-        <v>0</v>
-      </c>
+      <c r="N17"/>
       <c r="O17" t="s">
         <v>67</v>
       </c>
@@ -5972,9 +5934,7 @@
       <c r="M18">
         <v>16</v>
       </c>
-      <c r="N18">
-        <v>0</v>
-      </c>
+      <c r="N18"/>
       <c r="O18" t="s">
         <v>69</v>
       </c>
@@ -6022,9 +5982,7 @@
       <c r="M19">
         <v>15</v>
       </c>
-      <c r="N19">
-        <v>0</v>
-      </c>
+      <c r="N19"/>
       <c r="O19" t="s">
         <v>71</v>
       </c>
@@ -6072,9 +6030,7 @@
       <c r="M20">
         <v>15</v>
       </c>
-      <c r="N20">
-        <v>0</v>
-      </c>
+      <c r="N20"/>
       <c r="O20" t="s">
         <v>73</v>
       </c>
@@ -6122,9 +6078,7 @@
       <c r="M21">
         <v>14</v>
       </c>
-      <c r="N21">
-        <v>0</v>
-      </c>
+      <c r="N21"/>
       <c r="O21" t="s">
         <v>75</v>
       </c>
@@ -6172,9 +6126,7 @@
       <c r="M22">
         <v>13</v>
       </c>
-      <c r="N22">
-        <v>0</v>
-      </c>
+      <c r="N22"/>
       <c r="O22" t="s">
         <v>77</v>
       </c>
@@ -6222,9 +6174,7 @@
       <c r="M23">
         <v>13</v>
       </c>
-      <c r="N23">
-        <v>0</v>
-      </c>
+      <c r="N23"/>
       <c r="O23" t="s">
         <v>79</v>
       </c>
@@ -6272,9 +6222,7 @@
       <c r="M24">
         <v>15</v>
       </c>
-      <c r="N24">
-        <v>0</v>
-      </c>
+      <c r="N24"/>
       <c r="O24" t="s">
         <v>81</v>
       </c>
@@ -6322,9 +6270,7 @@
       <c r="M25">
         <v>13</v>
       </c>
-      <c r="N25">
-        <v>0</v>
-      </c>
+      <c r="N25"/>
       <c r="O25" t="s">
         <v>83</v>
       </c>
@@ -6372,9 +6318,7 @@
       <c r="M26">
         <v>12</v>
       </c>
-      <c r="N26">
-        <v>0</v>
-      </c>
+      <c r="N26"/>
       <c r="O26" t="s">
         <v>85</v>
       </c>
@@ -6422,9 +6366,7 @@
       <c r="M27">
         <v>13</v>
       </c>
-      <c r="N27">
-        <v>0</v>
-      </c>
+      <c r="N27"/>
       <c r="O27" t="s">
         <v>87</v>
       </c>
@@ -6472,9 +6414,7 @@
       <c r="M28">
         <v>12</v>
       </c>
-      <c r="N28">
-        <v>0</v>
-      </c>
+      <c r="N28"/>
       <c r="O28" t="s">
         <v>89</v>
       </c>
@@ -6522,9 +6462,7 @@
       <c r="M29">
         <v>12</v>
       </c>
-      <c r="N29">
-        <v>0</v>
-      </c>
+      <c r="N29"/>
       <c r="O29" t="s">
         <v>91</v>
       </c>
@@ -6572,9 +6510,7 @@
       <c r="M30">
         <v>13</v>
       </c>
-      <c r="N30">
-        <v>0</v>
-      </c>
+      <c r="N30"/>
       <c r="O30" t="s">
         <v>93</v>
       </c>
@@ -6622,9 +6558,7 @@
       <c r="M31">
         <v>13</v>
       </c>
-      <c r="N31">
-        <v>0</v>
-      </c>
+      <c r="N31"/>
       <c r="O31" t="s">
         <v>96</v>
       </c>
@@ -6672,9 +6606,7 @@
       <c r="M32">
         <v>14</v>
       </c>
-      <c r="N32">
-        <v>0</v>
-      </c>
+      <c r="N32"/>
       <c r="O32" t="s">
         <v>98</v>
       </c>
@@ -6722,9 +6654,7 @@
       <c r="M33">
         <v>11</v>
       </c>
-      <c r="N33">
-        <v>0</v>
-      </c>
+      <c r="N33"/>
       <c r="O33" t="s">
         <v>100</v>
       </c>
@@ -6772,9 +6702,7 @@
       <c r="M34">
         <v>13</v>
       </c>
-      <c r="N34">
-        <v>0</v>
-      </c>
+      <c r="N34"/>
       <c r="O34" t="s">
         <v>102</v>
       </c>
@@ -6822,9 +6750,7 @@
       <c r="M35">
         <v>10</v>
       </c>
-      <c r="N35">
-        <v>0</v>
-      </c>
+      <c r="N35"/>
       <c r="O35" t="s">
         <v>104</v>
       </c>
@@ -6872,9 +6798,7 @@
       <c r="M36">
         <v>10</v>
       </c>
-      <c r="N36">
-        <v>0</v>
-      </c>
+      <c r="N36"/>
       <c r="O36" t="s">
         <v>106</v>
       </c>
@@ -6922,9 +6846,7 @@
       <c r="M37">
         <v>10</v>
       </c>
-      <c r="N37">
-        <v>0</v>
-      </c>
+      <c r="N37"/>
       <c r="O37" t="s">
         <v>108</v>
       </c>
@@ -6972,9 +6894,7 @@
       <c r="M38">
         <v>11</v>
       </c>
-      <c r="N38">
-        <v>0</v>
-      </c>
+      <c r="N38"/>
       <c r="O38" t="s">
         <v>111</v>
       </c>
@@ -7022,9 +6942,7 @@
       <c r="M39">
         <v>13</v>
       </c>
-      <c r="N39">
-        <v>0</v>
-      </c>
+      <c r="N39"/>
       <c r="O39" t="s">
         <v>114</v>
       </c>
@@ -7072,9 +6990,7 @@
       <c r="M40">
         <v>24</v>
       </c>
-      <c r="N40">
-        <v>0</v>
-      </c>
+      <c r="N40"/>
       <c r="O40" t="s">
         <v>116</v>
       </c>
@@ -7122,9 +7038,7 @@
       <c r="M41">
         <v>19</v>
       </c>
-      <c r="N41">
-        <v>0</v>
-      </c>
+      <c r="N41"/>
       <c r="O41" t="s">
         <v>119</v>
       </c>
@@ -7172,9 +7086,7 @@
       <c r="M42">
         <v>14</v>
       </c>
-      <c r="N42">
-        <v>0</v>
-      </c>
+      <c r="N42"/>
       <c r="O42" t="s">
         <v>121</v>
       </c>
@@ -7222,9 +7134,7 @@
       <c r="M43">
         <v>11</v>
       </c>
-      <c r="N43">
-        <v>0</v>
-      </c>
+      <c r="N43"/>
       <c r="O43" t="s">
         <v>123</v>
       </c>
@@ -7272,9 +7182,7 @@
       <c r="M44">
         <v>18</v>
       </c>
-      <c r="N44">
-        <v>0</v>
-      </c>
+      <c r="N44"/>
       <c r="O44" t="s">
         <v>126</v>
       </c>
@@ -7322,9 +7230,7 @@
       <c r="M45">
         <v>13</v>
       </c>
-      <c r="N45">
-        <v>0</v>
-      </c>
+      <c r="N45"/>
       <c r="O45" t="s">
         <v>128</v>
       </c>
@@ -7372,9 +7278,7 @@
       <c r="M46">
         <v>98</v>
       </c>
-      <c r="N46">
-        <v>0</v>
-      </c>
+      <c r="N46"/>
       <c r="O46" t="s">
         <v>132</v>
       </c>
@@ -7422,9 +7326,7 @@
       <c r="M47">
         <v>91</v>
       </c>
-      <c r="N47">
-        <v>0</v>
-      </c>
+      <c r="N47"/>
       <c r="O47" t="s">
         <v>135</v>
       </c>
@@ -7472,9 +7374,7 @@
       <c r="M48">
         <v>24</v>
       </c>
-      <c r="N48">
-        <v>0</v>
-      </c>
+      <c r="N48"/>
       <c r="O48" t="s">
         <v>137</v>
       </c>
@@ -7522,9 +7422,7 @@
       <c r="M49">
         <v>32</v>
       </c>
-      <c r="N49">
-        <v>0</v>
-      </c>
+      <c r="N49"/>
       <c r="O49" t="s">
         <v>139</v>
       </c>
@@ -7572,9 +7470,7 @@
       <c r="M50">
         <v>27</v>
       </c>
-      <c r="N50">
-        <v>0</v>
-      </c>
+      <c r="N50"/>
       <c r="O50" t="s">
         <v>142</v>
       </c>
@@ -7622,9 +7518,7 @@
       <c r="M51">
         <v>28</v>
       </c>
-      <c r="N51">
-        <v>0</v>
-      </c>
+      <c r="N51"/>
       <c r="O51" t="s">
         <v>145</v>
       </c>
@@ -7672,9 +7566,7 @@
       <c r="M52">
         <v>41</v>
       </c>
-      <c r="N52">
-        <v>0</v>
-      </c>
+      <c r="N52"/>
       <c r="O52" t="s">
         <v>147</v>
       </c>
@@ -7722,9 +7614,7 @@
       <c r="M53">
         <v>13</v>
       </c>
-      <c r="N53">
-        <v>0</v>
-      </c>
+      <c r="N53"/>
       <c r="O53" t="s">
         <v>149</v>
       </c>
@@ -7772,9 +7662,7 @@
       <c r="M54">
         <v>11</v>
       </c>
-      <c r="N54">
-        <v>0</v>
-      </c>
+      <c r="N54"/>
       <c r="O54" t="s">
         <v>152</v>
       </c>
@@ -7822,9 +7710,7 @@
       <c r="M55">
         <v>10</v>
       </c>
-      <c r="N55">
-        <v>0</v>
-      </c>
+      <c r="N55"/>
       <c r="O55" t="s">
         <v>154</v>
       </c>
@@ -7872,9 +7758,7 @@
       <c r="M56">
         <v>9</v>
       </c>
-      <c r="N56">
-        <v>0</v>
-      </c>
+      <c r="N56"/>
       <c r="O56" t="s">
         <v>156</v>
       </c>
@@ -7922,9 +7806,7 @@
       <c r="M57">
         <v>13</v>
       </c>
-      <c r="N57">
-        <v>0</v>
-      </c>
+      <c r="N57"/>
       <c r="O57" t="s">
         <v>159</v>
       </c>
@@ -7972,9 +7854,7 @@
       <c r="M58">
         <v>8</v>
       </c>
-      <c r="N58">
-        <v>0</v>
-      </c>
+      <c r="N58"/>
       <c r="O58" t="s">
         <v>161</v>
       </c>
@@ -8022,9 +7902,7 @@
       <c r="M59">
         <v>11</v>
       </c>
-      <c r="N59">
-        <v>0</v>
-      </c>
+      <c r="N59"/>
       <c r="O59" t="s">
         <v>163</v>
       </c>
@@ -8072,9 +7950,7 @@
       <c r="M60">
         <v>9</v>
       </c>
-      <c r="N60">
-        <v>0</v>
-      </c>
+      <c r="N60"/>
       <c r="O60" t="s">
         <v>165</v>
       </c>
@@ -8122,9 +7998,7 @@
       <c r="M61">
         <v>14</v>
       </c>
-      <c r="N61">
-        <v>0</v>
-      </c>
+      <c r="N61"/>
       <c r="O61" t="s">
         <v>167</v>
       </c>
@@ -8172,9 +8046,7 @@
       <c r="M62">
         <v>14</v>
       </c>
-      <c r="N62">
-        <v>0</v>
-      </c>
+      <c r="N62"/>
       <c r="O62" t="s">
         <v>169</v>
       </c>
@@ -8222,9 +8094,7 @@
       <c r="M63">
         <v>18</v>
       </c>
-      <c r="N63">
-        <v>0</v>
-      </c>
+      <c r="N63"/>
       <c r="O63" t="s">
         <v>171</v>
       </c>
@@ -8272,9 +8142,7 @@
       <c r="M64">
         <v>19</v>
       </c>
-      <c r="N64">
-        <v>0</v>
-      </c>
+      <c r="N64"/>
       <c r="O64" t="s">
         <v>173</v>
       </c>
@@ -8322,9 +8190,7 @@
       <c r="M65">
         <v>18</v>
       </c>
-      <c r="N65">
-        <v>0</v>
-      </c>
+      <c r="N65"/>
       <c r="O65" t="s">
         <v>175</v>
       </c>
@@ -8372,9 +8238,7 @@
       <c r="M66">
         <v>23</v>
       </c>
-      <c r="N66">
-        <v>0</v>
-      </c>
+      <c r="N66"/>
       <c r="O66" t="s">
         <v>177</v>
       </c>
@@ -8422,9 +8286,7 @@
       <c r="M67">
         <v>8</v>
       </c>
-      <c r="N67">
-        <v>0</v>
-      </c>
+      <c r="N67"/>
       <c r="O67" t="s">
         <v>179</v>
       </c>
@@ -8472,9 +8334,7 @@
       <c r="M68">
         <v>10</v>
       </c>
-      <c r="N68">
-        <v>0</v>
-      </c>
+      <c r="N68"/>
       <c r="O68" t="s">
         <v>181</v>
       </c>
@@ -8522,9 +8382,7 @@
       <c r="M69">
         <v>7</v>
       </c>
-      <c r="N69">
-        <v>0</v>
-      </c>
+      <c r="N69"/>
       <c r="O69" t="s">
         <v>183</v>
       </c>
@@ -8572,9 +8430,7 @@
       <c r="M70">
         <v>10</v>
       </c>
-      <c r="N70">
-        <v>0</v>
-      </c>
+      <c r="N70"/>
       <c r="O70" t="s">
         <v>185</v>
       </c>
@@ -8622,9 +8478,7 @@
       <c r="M71">
         <v>8</v>
       </c>
-      <c r="N71">
-        <v>0</v>
-      </c>
+      <c r="N71"/>
       <c r="O71" t="s">
         <v>187</v>
       </c>
@@ -8672,9 +8526,7 @@
       <c r="M72">
         <v>6</v>
       </c>
-      <c r="N72">
-        <v>0</v>
-      </c>
+      <c r="N72"/>
       <c r="O72" t="s">
         <v>189</v>
       </c>
@@ -8722,9 +8574,7 @@
       <c r="M73">
         <v>22</v>
       </c>
-      <c r="N73">
-        <v>0</v>
-      </c>
+      <c r="N73"/>
       <c r="O73" t="s">
         <v>191</v>
       </c>
@@ -8772,9 +8622,7 @@
       <c r="M74">
         <v>9</v>
       </c>
-      <c r="N74">
-        <v>0</v>
-      </c>
+      <c r="N74"/>
       <c r="O74" t="s">
         <v>193</v>
       </c>
@@ -8822,9 +8670,7 @@
       <c r="M75">
         <v>10</v>
       </c>
-      <c r="N75">
-        <v>0</v>
-      </c>
+      <c r="N75"/>
       <c r="O75" t="s">
         <v>195</v>
       </c>
@@ -8872,9 +8718,7 @@
       <c r="M76">
         <v>7</v>
       </c>
-      <c r="N76">
-        <v>0</v>
-      </c>
+      <c r="N76"/>
       <c r="O76" t="s">
         <v>197</v>
       </c>
@@ -8922,9 +8766,7 @@
       <c r="M77">
         <v>11</v>
       </c>
-      <c r="N77">
-        <v>0</v>
-      </c>
+      <c r="N77"/>
       <c r="O77" t="s">
         <v>199</v>
       </c>
@@ -8972,9 +8814,7 @@
       <c r="M78">
         <v>8</v>
       </c>
-      <c r="N78">
-        <v>0</v>
-      </c>
+      <c r="N78"/>
       <c r="O78" t="s">
         <v>201</v>
       </c>
@@ -9022,9 +8862,7 @@
       <c r="M79">
         <v>8</v>
       </c>
-      <c r="N79">
-        <v>0</v>
-      </c>
+      <c r="N79"/>
       <c r="O79" t="s">
         <v>203</v>
       </c>
@@ -9072,9 +8910,7 @@
       <c r="M80">
         <v>8</v>
       </c>
-      <c r="N80">
-        <v>0</v>
-      </c>
+      <c r="N80"/>
       <c r="O80" t="s">
         <v>206</v>
       </c>
@@ -9122,9 +8958,7 @@
       <c r="M81">
         <v>16</v>
       </c>
-      <c r="N81">
-        <v>0</v>
-      </c>
+      <c r="N81"/>
       <c r="O81" t="s">
         <v>208</v>
       </c>
@@ -9172,9 +9006,7 @@
       <c r="M82">
         <v>8</v>
       </c>
-      <c r="N82">
-        <v>0</v>
-      </c>
+      <c r="N82"/>
       <c r="O82" t="s">
         <v>210</v>
       </c>
@@ -9222,9 +9054,7 @@
       <c r="M83">
         <v>7</v>
       </c>
-      <c r="N83">
-        <v>0</v>
-      </c>
+      <c r="N83"/>
       <c r="O83" t="s">
         <v>212</v>
       </c>
@@ -9272,9 +9102,7 @@
       <c r="M84">
         <v>9</v>
       </c>
-      <c r="N84">
-        <v>0</v>
-      </c>
+      <c r="N84"/>
       <c r="O84" t="s">
         <v>214</v>
       </c>
@@ -9322,9 +9150,7 @@
       <c r="M85">
         <v>7</v>
       </c>
-      <c r="N85">
-        <v>0</v>
-      </c>
+      <c r="N85"/>
       <c r="O85" t="s">
         <v>216</v>
       </c>
@@ -9372,9 +9198,7 @@
       <c r="M86">
         <v>7</v>
       </c>
-      <c r="N86">
-        <v>0</v>
-      </c>
+      <c r="N86"/>
       <c r="O86" t="s">
         <v>218</v>
       </c>
@@ -9422,9 +9246,7 @@
       <c r="M87">
         <v>8</v>
       </c>
-      <c r="N87">
-        <v>0</v>
-      </c>
+      <c r="N87"/>
       <c r="O87" t="s">
         <v>220</v>
       </c>
@@ -9472,9 +9294,7 @@
       <c r="M88">
         <v>7</v>
       </c>
-      <c r="N88">
-        <v>0</v>
-      </c>
+      <c r="N88"/>
       <c r="O88" t="s">
         <v>222</v>
       </c>
@@ -9522,9 +9342,7 @@
       <c r="M89">
         <v>7</v>
       </c>
-      <c r="N89">
-        <v>0</v>
-      </c>
+      <c r="N89"/>
       <c r="O89" t="s">
         <v>224</v>
       </c>
@@ -9572,9 +9390,7 @@
       <c r="M90">
         <v>13</v>
       </c>
-      <c r="N90">
-        <v>0</v>
-      </c>
+      <c r="N90"/>
       <c r="O90" t="s">
         <v>227</v>
       </c>
@@ -9622,9 +9438,7 @@
       <c r="M91">
         <v>16</v>
       </c>
-      <c r="N91">
-        <v>0</v>
-      </c>
+      <c r="N91"/>
       <c r="O91" t="s">
         <v>230</v>
       </c>
@@ -9672,9 +9486,7 @@
       <c r="M92">
         <v>13</v>
       </c>
-      <c r="N92">
-        <v>0</v>
-      </c>
+      <c r="N92"/>
       <c r="O92" t="s">
         <v>232</v>
       </c>
@@ -9722,9 +9534,7 @@
       <c r="M93">
         <v>7</v>
       </c>
-      <c r="N93">
-        <v>0</v>
-      </c>
+      <c r="N93"/>
       <c r="O93" t="s">
         <v>234</v>
       </c>
@@ -9772,9 +9582,7 @@
       <c r="M94">
         <v>7</v>
       </c>
-      <c r="N94">
-        <v>0</v>
-      </c>
+      <c r="N94"/>
       <c r="O94" t="s">
         <v>236</v>
       </c>
@@ -9822,9 +9630,7 @@
       <c r="M95">
         <v>7</v>
       </c>
-      <c r="N95">
-        <v>0</v>
-      </c>
+      <c r="N95"/>
       <c r="O95" t="s">
         <v>238</v>
       </c>
@@ -9872,9 +9678,7 @@
       <c r="M96">
         <v>7</v>
       </c>
-      <c r="N96">
-        <v>0</v>
-      </c>
+      <c r="N96"/>
       <c r="O96" t="s">
         <v>240</v>
       </c>
@@ -9922,9 +9726,7 @@
       <c r="M97">
         <v>7</v>
       </c>
-      <c r="N97">
-        <v>0</v>
-      </c>
+      <c r="N97"/>
       <c r="O97" t="s">
         <v>242</v>
       </c>
@@ -9972,9 +9774,7 @@
       <c r="M98">
         <v>11</v>
       </c>
-      <c r="N98">
-        <v>0</v>
-      </c>
+      <c r="N98"/>
       <c r="O98" t="s">
         <v>243</v>
       </c>
@@ -10022,9 +9822,7 @@
       <c r="M99">
         <v>10</v>
       </c>
-      <c r="N99">
-        <v>0</v>
-      </c>
+      <c r="N99"/>
       <c r="O99" t="s">
         <v>245</v>
       </c>
@@ -10072,9 +9870,7 @@
       <c r="M100">
         <v>9</v>
       </c>
-      <c r="N100">
-        <v>0</v>
-      </c>
+      <c r="N100"/>
       <c r="O100" t="s">
         <v>247</v>
       </c>
@@ -10122,9 +9918,7 @@
       <c r="M101">
         <v>13</v>
       </c>
-      <c r="N101">
-        <v>0</v>
-      </c>
+      <c r="N101"/>
       <c r="O101" t="s">
         <v>249</v>
       </c>
@@ -10172,9 +9966,7 @@
       <c r="M102">
         <v>2</v>
       </c>
-      <c r="N102">
-        <v>0</v>
-      </c>
+      <c r="N102"/>
       <c r="O102" t="s">
         <v>251</v>
       </c>
@@ -10222,9 +10014,7 @@
       <c r="M103">
         <v>2</v>
       </c>
-      <c r="N103">
-        <v>0</v>
-      </c>
+      <c r="N103"/>
       <c r="O103" t="s">
         <v>253</v>
       </c>
@@ -10272,9 +10062,7 @@
       <c r="M104">
         <v>2</v>
       </c>
-      <c r="N104">
-        <v>0</v>
-      </c>
+      <c r="N104"/>
       <c r="O104" t="s">
         <v>255</v>
       </c>
@@ -10322,9 +10110,7 @@
       <c r="M105">
         <v>2</v>
       </c>
-      <c r="N105">
-        <v>0</v>
-      </c>
+      <c r="N105"/>
       <c r="O105" t="s">
         <v>257</v>
       </c>
@@ -10372,9 +10158,7 @@
       <c r="M106">
         <v>7</v>
       </c>
-      <c r="N106">
-        <v>0</v>
-      </c>
+      <c r="N106"/>
       <c r="O106" t="s">
         <v>259</v>
       </c>
@@ -10422,9 +10206,7 @@
       <c r="M107">
         <v>1</v>
       </c>
-      <c r="N107">
-        <v>0</v>
-      </c>
+      <c r="N107"/>
       <c r="O107" t="s">
         <v>261</v>
       </c>
@@ -10472,9 +10254,7 @@
       <c r="M108">
         <v>2</v>
       </c>
-      <c r="N108">
-        <v>0</v>
-      </c>
+      <c r="N108"/>
       <c r="O108" t="s">
         <v>263</v>
       </c>
@@ -10522,9 +10302,7 @@
       <c r="M109">
         <v>2</v>
       </c>
-      <c r="N109">
-        <v>0</v>
-      </c>
+      <c r="N109"/>
       <c r="O109" t="s">
         <v>265</v>
       </c>
@@ -10572,9 +10350,7 @@
       <c r="M110">
         <v>1</v>
       </c>
-      <c r="N110">
-        <v>0</v>
-      </c>
+      <c r="N110"/>
       <c r="O110" t="s">
         <v>267</v>
       </c>
@@ -10622,9 +10398,7 @@
       <c r="M111">
         <v>2</v>
       </c>
-      <c r="N111">
-        <v>0</v>
-      </c>
+      <c r="N111"/>
       <c r="O111" t="s">
         <v>269</v>
       </c>
@@ -10672,9 +10446,7 @@
       <c r="M112">
         <v>4</v>
       </c>
-      <c r="N112">
-        <v>0</v>
-      </c>
+      <c r="N112"/>
       <c r="O112" t="s">
         <v>271</v>
       </c>
@@ -10722,9 +10494,7 @@
       <c r="M113">
         <v>3</v>
       </c>
-      <c r="N113">
-        <v>0</v>
-      </c>
+      <c r="N113"/>
       <c r="O113" t="s">
         <v>273</v>
       </c>
@@ -10772,9 +10542,7 @@
       <c r="M114">
         <v>7</v>
       </c>
-      <c r="N114">
-        <v>0</v>
-      </c>
+      <c r="N114"/>
       <c r="O114" t="s">
         <v>275</v>
       </c>
@@ -10822,9 +10590,7 @@
       <c r="M115">
         <v>1</v>
       </c>
-      <c r="N115">
-        <v>0</v>
-      </c>
+      <c r="N115"/>
       <c r="O115" t="s">
         <v>277</v>
       </c>
@@ -10872,9 +10638,7 @@
       <c r="M116">
         <v>2</v>
       </c>
-      <c r="N116">
-        <v>0</v>
-      </c>
+      <c r="N116"/>
       <c r="O116" t="s">
         <v>279</v>
       </c>
@@ -10922,9 +10686,7 @@
       <c r="M117">
         <v>8</v>
       </c>
-      <c r="N117">
-        <v>0</v>
-      </c>
+      <c r="N117"/>
       <c r="O117" t="s">
         <v>281</v>
       </c>
@@ -10972,9 +10734,7 @@
       <c r="M118">
         <v>1</v>
       </c>
-      <c r="N118">
-        <v>0</v>
-      </c>
+      <c r="N118"/>
       <c r="O118" t="s">
         <v>283</v>
       </c>
@@ -11022,9 +10782,7 @@
       <c r="M119">
         <v>2</v>
       </c>
-      <c r="N119">
-        <v>0</v>
-      </c>
+      <c r="N119"/>
       <c r="O119" t="s">
         <v>285</v>
       </c>
@@ -11072,9 +10830,7 @@
       <c r="M120">
         <v>2</v>
       </c>
-      <c r="N120">
-        <v>0</v>
-      </c>
+      <c r="N120"/>
       <c r="O120" t="s">
         <v>287</v>
       </c>
@@ -11122,9 +10878,7 @@
       <c r="M121">
         <v>1</v>
       </c>
-      <c r="N121">
-        <v>0</v>
-      </c>
+      <c r="N121"/>
       <c r="O121" t="s">
         <v>289</v>
       </c>
@@ -11172,9 +10926,7 @@
       <c r="M122">
         <v>1</v>
       </c>
-      <c r="N122">
-        <v>0</v>
-      </c>
+      <c r="N122"/>
       <c r="O122" t="s">
         <v>291</v>
       </c>
@@ -11222,9 +10974,7 @@
       <c r="M123">
         <v>2</v>
       </c>
-      <c r="N123">
-        <v>0</v>
-      </c>
+      <c r="N123"/>
       <c r="O123" t="s">
         <v>293</v>
       </c>
@@ -11272,9 +11022,7 @@
       <c r="M124">
         <v>1</v>
       </c>
-      <c r="N124">
-        <v>0</v>
-      </c>
+      <c r="N124"/>
       <c r="O124" t="s">
         <v>295</v>
       </c>
@@ -11322,9 +11070,7 @@
       <c r="M125">
         <v>1</v>
       </c>
-      <c r="N125">
-        <v>0</v>
-      </c>
+      <c r="N125"/>
       <c r="O125" t="s">
         <v>297</v>
       </c>
@@ -11372,9 +11118,7 @@
       <c r="M126">
         <v>1</v>
       </c>
-      <c r="N126">
-        <v>0</v>
-      </c>
+      <c r="N126"/>
       <c r="O126" t="s">
         <v>299</v>
       </c>
@@ -11422,9 +11166,7 @@
       <c r="M127">
         <v>1</v>
       </c>
-      <c r="N127">
-        <v>0</v>
-      </c>
+      <c r="N127"/>
       <c r="O127" t="s">
         <v>301</v>
       </c>
@@ -11472,9 +11214,7 @@
       <c r="M128">
         <v>2</v>
       </c>
-      <c r="N128">
-        <v>0</v>
-      </c>
+      <c r="N128"/>
       <c r="O128" t="s">
         <v>303</v>
       </c>
@@ -11522,9 +11262,7 @@
       <c r="M129">
         <v>1</v>
       </c>
-      <c r="N129">
-        <v>0</v>
-      </c>
+      <c r="N129"/>
       <c r="O129" t="s">
         <v>305</v>
       </c>
@@ -11572,9 +11310,7 @@
       <c r="M130">
         <v>1</v>
       </c>
-      <c r="N130">
-        <v>0</v>
-      </c>
+      <c r="N130"/>
       <c r="O130" t="s">
         <v>307</v>
       </c>
@@ -11622,9 +11358,7 @@
       <c r="M131">
         <v>1</v>
       </c>
-      <c r="N131">
-        <v>0</v>
-      </c>
+      <c r="N131"/>
       <c r="O131" t="s">
         <v>309</v>
       </c>
@@ -11672,9 +11406,7 @@
       <c r="M132">
         <v>2</v>
       </c>
-      <c r="N132">
-        <v>0</v>
-      </c>
+      <c r="N132"/>
       <c r="O132" t="s">
         <v>311</v>
       </c>
@@ -11722,9 +11454,7 @@
       <c r="M133">
         <v>1</v>
       </c>
-      <c r="N133">
-        <v>0</v>
-      </c>
+      <c r="N133"/>
       <c r="O133" t="s">
         <v>313</v>
       </c>
@@ -11772,9 +11502,7 @@
       <c r="M134">
         <v>1</v>
       </c>
-      <c r="N134">
-        <v>0</v>
-      </c>
+      <c r="N134"/>
       <c r="O134" t="s">
         <v>314</v>
       </c>
@@ -11822,9 +11550,7 @@
       <c r="M135">
         <v>1</v>
       </c>
-      <c r="N135">
-        <v>0</v>
-      </c>
+      <c r="N135"/>
       <c r="O135" t="s">
         <v>316</v>
       </c>
@@ -11872,9 +11598,7 @@
       <c r="M136">
         <v>1</v>
       </c>
-      <c r="N136">
-        <v>0</v>
-      </c>
+      <c r="N136"/>
       <c r="O136" t="s">
         <v>317</v>
       </c>
@@ -11922,9 +11646,7 @@
       <c r="M137">
         <v>1</v>
       </c>
-      <c r="N137">
-        <v>0</v>
-      </c>
+      <c r="N137"/>
       <c r="O137" t="s">
         <v>319</v>
       </c>
@@ -11972,9 +11694,7 @@
       <c r="M138">
         <v>28</v>
       </c>
-      <c r="N138">
-        <v>0</v>
-      </c>
+      <c r="N138"/>
       <c r="O138" t="s">
         <v>323</v>
       </c>
@@ -12022,9 +11742,7 @@
       <c r="M139">
         <v>25</v>
       </c>
-      <c r="N139">
-        <v>0</v>
-      </c>
+      <c r="N139"/>
       <c r="O139" t="s">
         <v>325</v>
       </c>
@@ -12072,9 +11790,7 @@
       <c r="M140">
         <v>20</v>
       </c>
-      <c r="N140">
-        <v>0</v>
-      </c>
+      <c r="N140"/>
       <c r="O140" t="s">
         <v>327</v>
       </c>
@@ -12122,9 +11838,7 @@
       <c r="M141">
         <v>14</v>
       </c>
-      <c r="N141">
-        <v>0</v>
-      </c>
+      <c r="N141"/>
       <c r="O141" t="s">
         <v>329</v>
       </c>
@@ -12172,9 +11886,7 @@
       <c r="M142">
         <v>9</v>
       </c>
-      <c r="N142">
-        <v>0</v>
-      </c>
+      <c r="N142"/>
       <c r="O142" t="s">
         <v>331</v>
       </c>
@@ -12222,9 +11934,7 @@
       <c r="M143">
         <v>4</v>
       </c>
-      <c r="N143">
-        <v>0</v>
-      </c>
+      <c r="N143"/>
       <c r="O143" t="s">
         <v>333</v>
       </c>
@@ -12272,9 +11982,7 @@
       <c r="M144">
         <v>8</v>
       </c>
-      <c r="N144">
-        <v>0</v>
-      </c>
+      <c r="N144"/>
       <c r="O144" t="s">
         <v>335</v>
       </c>
@@ -12322,9 +12030,7 @@
       <c r="M145">
         <v>8</v>
       </c>
-      <c r="N145">
-        <v>0</v>
-      </c>
+      <c r="N145"/>
       <c r="O145" t="s">
         <v>336</v>
       </c>
@@ -12372,9 +12078,7 @@
       <c r="M146">
         <v>10</v>
       </c>
-      <c r="N146">
-        <v>0</v>
-      </c>
+      <c r="N146"/>
       <c r="O146" t="s">
         <v>338</v>
       </c>
@@ -12422,9 +12126,7 @@
       <c r="M147">
         <v>14</v>
       </c>
-      <c r="N147">
-        <v>0</v>
-      </c>
+      <c r="N147"/>
       <c r="O147" t="s">
         <v>340</v>
       </c>
@@ -12472,9 +12174,7 @@
       <c r="M148">
         <v>5</v>
       </c>
-      <c r="N148">
-        <v>0</v>
-      </c>
+      <c r="N148"/>
       <c r="O148" t="s">
         <v>342</v>
       </c>
@@ -12522,9 +12222,7 @@
       <c r="M149">
         <v>4</v>
       </c>
-      <c r="N149">
-        <v>0</v>
-      </c>
+      <c r="N149"/>
       <c r="O149" t="s">
         <v>344</v>
       </c>
@@ -12572,9 +12270,7 @@
       <c r="M150">
         <v>3</v>
       </c>
-      <c r="N150">
-        <v>0</v>
-      </c>
+      <c r="N150"/>
       <c r="O150" t="s">
         <v>346</v>
       </c>
@@ -12622,9 +12318,7 @@
       <c r="M151">
         <v>22</v>
       </c>
-      <c r="N151">
-        <v>0</v>
-      </c>
+      <c r="N151"/>
       <c r="O151" t="s">
         <v>348</v>
       </c>
@@ -12672,9 +12366,7 @@
       <c r="M152">
         <v>4</v>
       </c>
-      <c r="N152">
-        <v>0</v>
-      </c>
+      <c r="N152"/>
       <c r="O152" t="s">
         <v>350</v>
       </c>
@@ -12722,9 +12414,7 @@
       <c r="M153">
         <v>3</v>
       </c>
-      <c r="N153">
-        <v>0</v>
-      </c>
+      <c r="N153"/>
       <c r="O153" t="s">
         <v>352</v>
       </c>
@@ -12772,9 +12462,7 @@
       <c r="M154">
         <v>2</v>
       </c>
-      <c r="N154">
-        <v>0</v>
-      </c>
+      <c r="N154"/>
       <c r="O154" t="s">
         <v>354</v>
       </c>
@@ -12822,9 +12510,7 @@
       <c r="M155">
         <v>1</v>
       </c>
-      <c r="N155">
-        <v>0</v>
-      </c>
+      <c r="N155"/>
       <c r="O155" t="s">
         <v>356</v>
       </c>
@@ -12872,9 +12558,7 @@
       <c r="M156">
         <v>2</v>
       </c>
-      <c r="N156">
-        <v>0</v>
-      </c>
+      <c r="N156"/>
       <c r="O156" t="s">
         <v>358</v>
       </c>
@@ -12922,9 +12606,7 @@
       <c r="M157">
         <v>3</v>
       </c>
-      <c r="N157">
-        <v>0</v>
-      </c>
+      <c r="N157"/>
       <c r="O157" t="s">
         <v>360</v>
       </c>
@@ -12972,9 +12654,7 @@
       <c r="M158">
         <v>4</v>
       </c>
-      <c r="N158">
-        <v>0</v>
-      </c>
+      <c r="N158"/>
       <c r="O158" t="s">
         <v>362</v>
       </c>
@@ -13022,9 +12702,7 @@
       <c r="M159">
         <v>2</v>
       </c>
-      <c r="N159">
-        <v>0</v>
-      </c>
+      <c r="N159"/>
       <c r="O159" t="s">
         <v>364</v>
       </c>
@@ -13072,9 +12750,7 @@
       <c r="M160">
         <v>3</v>
       </c>
-      <c r="N160">
-        <v>0</v>
-      </c>
+      <c r="N160"/>
       <c r="O160" t="s">
         <v>366</v>
       </c>
@@ -13122,9 +12798,7 @@
       <c r="M161">
         <v>1</v>
       </c>
-      <c r="N161">
-        <v>0</v>
-      </c>
+      <c r="N161"/>
       <c r="O161" t="s">
         <v>368</v>
       </c>
@@ -13172,9 +12846,7 @@
       <c r="M162">
         <v>2</v>
       </c>
-      <c r="N162">
-        <v>0</v>
-      </c>
+      <c r="N162"/>
       <c r="O162" t="s">
         <v>370</v>
       </c>
@@ -13222,9 +12894,7 @@
       <c r="M163">
         <v>1</v>
       </c>
-      <c r="N163">
-        <v>0</v>
-      </c>
+      <c r="N163"/>
       <c r="O163" t="s">
         <v>372</v>
       </c>
@@ -13272,9 +12942,7 @@
       <c r="M164">
         <v>1</v>
       </c>
-      <c r="N164">
-        <v>0</v>
-      </c>
+      <c r="N164"/>
       <c r="O164" t="s">
         <v>374</v>
       </c>
@@ -13322,9 +12990,7 @@
       <c r="M165">
         <v>1</v>
       </c>
-      <c r="N165">
-        <v>0</v>
-      </c>
+      <c r="N165"/>
       <c r="O165" t="s">
         <v>376</v>
       </c>
@@ -13372,9 +13038,7 @@
       <c r="M166">
         <v>4</v>
       </c>
-      <c r="N166">
-        <v>0</v>
-      </c>
+      <c r="N166"/>
       <c r="O166" t="s">
         <v>378</v>
       </c>
@@ -13422,9 +13086,7 @@
       <c r="M167">
         <v>3</v>
       </c>
-      <c r="N167">
-        <v>0</v>
-      </c>
+      <c r="N167"/>
       <c r="O167" t="s">
         <v>380</v>
       </c>
@@ -13472,9 +13134,7 @@
       <c r="M168">
         <v>3</v>
       </c>
-      <c r="N168">
-        <v>0</v>
-      </c>
+      <c r="N168"/>
       <c r="O168" t="s">
         <v>382</v>
       </c>
@@ -13522,9 +13182,7 @@
       <c r="M169">
         <v>3</v>
       </c>
-      <c r="N169">
-        <v>0</v>
-      </c>
+      <c r="N169"/>
       <c r="O169" t="s">
         <v>384</v>
       </c>
@@ -13572,9 +13230,7 @@
       <c r="M170">
         <v>1</v>
       </c>
-      <c r="N170">
-        <v>0</v>
-      </c>
+      <c r="N170"/>
       <c r="O170" t="s">
         <v>386</v>
       </c>
@@ -13622,9 +13278,7 @@
       <c r="M171">
         <v>1</v>
       </c>
-      <c r="N171">
-        <v>0</v>
-      </c>
+      <c r="N171"/>
       <c r="O171" t="s">
         <v>388</v>
       </c>
@@ -13672,9 +13326,7 @@
       <c r="M172">
         <v>4</v>
       </c>
-      <c r="N172">
-        <v>0</v>
-      </c>
+      <c r="N172"/>
       <c r="O172" t="s">
         <v>390</v>
       </c>
@@ -13722,9 +13374,7 @@
       <c r="M173">
         <v>4</v>
       </c>
-      <c r="N173">
-        <v>0</v>
-      </c>
+      <c r="N173"/>
       <c r="O173" t="s">
         <v>392</v>
       </c>
@@ -13772,9 +13422,7 @@
       <c r="M174">
         <v>1</v>
       </c>
-      <c r="N174">
-        <v>0</v>
-      </c>
+      <c r="N174"/>
       <c r="O174" t="s">
         <v>394</v>
       </c>
@@ -13822,9 +13470,7 @@
       <c r="M175">
         <v>2</v>
       </c>
-      <c r="N175">
-        <v>0</v>
-      </c>
+      <c r="N175"/>
       <c r="O175" t="s">
         <v>396</v>
       </c>
@@ -13872,9 +13518,7 @@
       <c r="M176">
         <v>1</v>
       </c>
-      <c r="N176">
-        <v>0</v>
-      </c>
+      <c r="N176"/>
       <c r="O176" t="s">
         <v>398</v>
       </c>
@@ -13922,9 +13566,7 @@
       <c r="M177">
         <v>1</v>
       </c>
-      <c r="N177">
-        <v>0</v>
-      </c>
+      <c r="N177"/>
       <c r="O177" t="s">
         <v>400</v>
       </c>
@@ -13972,9 +13614,7 @@
       <c r="M178">
         <v>1</v>
       </c>
-      <c r="N178">
-        <v>0</v>
-      </c>
+      <c r="N178"/>
       <c r="O178" t="s">
         <v>402</v>
       </c>
@@ -14022,9 +13662,7 @@
       <c r="M179">
         <v>1</v>
       </c>
-      <c r="N179">
-        <v>0</v>
-      </c>
+      <c r="N179"/>
       <c r="O179" t="s">
         <v>404</v>
       </c>
@@ -14072,9 +13710,7 @@
       <c r="M180">
         <v>2</v>
       </c>
-      <c r="N180">
-        <v>0</v>
-      </c>
+      <c r="N180"/>
       <c r="O180" t="s">
         <v>406</v>
       </c>
@@ -14122,9 +13758,7 @@
       <c r="M181">
         <v>2</v>
       </c>
-      <c r="N181">
-        <v>0</v>
-      </c>
+      <c r="N181"/>
       <c r="O181" t="s">
         <v>408</v>
       </c>
@@ -14172,9 +13806,7 @@
       <c r="M182">
         <v>1</v>
       </c>
-      <c r="N182">
-        <v>0</v>
-      </c>
+      <c r="N182"/>
       <c r="O182" t="s">
         <v>410</v>
       </c>
@@ -14222,9 +13854,7 @@
       <c r="M183">
         <v>1</v>
       </c>
-      <c r="N183">
-        <v>0</v>
-      </c>
+      <c r="N183"/>
       <c r="O183" t="s">
         <v>412</v>
       </c>
@@ -14272,9 +13902,7 @@
       <c r="M184">
         <v>1</v>
       </c>
-      <c r="N184">
-        <v>0</v>
-      </c>
+      <c r="N184"/>
       <c r="O184" t="s">
         <v>414</v>
       </c>
@@ -14322,9 +13950,7 @@
       <c r="M185">
         <v>2</v>
       </c>
-      <c r="N185">
-        <v>0</v>
-      </c>
+      <c r="N185"/>
       <c r="O185" t="s">
         <v>417</v>
       </c>
@@ -14372,9 +13998,7 @@
       <c r="M186">
         <v>8</v>
       </c>
-      <c r="N186">
-        <v>0</v>
-      </c>
+      <c r="N186"/>
       <c r="O186" t="s">
         <v>420</v>
       </c>
@@ -14422,9 +14046,7 @@
       <c r="M187">
         <v>1</v>
       </c>
-      <c r="N187">
-        <v>0</v>
-      </c>
+      <c r="N187"/>
       <c r="O187" t="s">
         <v>422</v>
       </c>
@@ -14472,9 +14094,7 @@
       <c r="M188">
         <v>1</v>
       </c>
-      <c r="N188">
-        <v>0</v>
-      </c>
+      <c r="N188"/>
       <c r="O188" t="s">
         <v>424</v>
       </c>
@@ -14522,9 +14142,7 @@
       <c r="M189">
         <v>3</v>
       </c>
-      <c r="N189">
-        <v>0</v>
-      </c>
+      <c r="N189"/>
       <c r="O189" t="s">
         <v>426</v>
       </c>
@@ -14572,9 +14190,7 @@
       <c r="M190">
         <v>9</v>
       </c>
-      <c r="N190">
-        <v>0</v>
-      </c>
+      <c r="N190"/>
       <c r="O190" t="s">
         <v>429</v>
       </c>
@@ -14622,9 +14238,7 @@
       <c r="M191">
         <v>1</v>
       </c>
-      <c r="N191">
-        <v>0</v>
-      </c>
+      <c r="N191"/>
       <c r="O191" t="s">
         <v>431</v>
       </c>
@@ -14672,9 +14286,7 @@
       <c r="M192">
         <v>4</v>
       </c>
-      <c r="N192">
-        <v>0</v>
-      </c>
+      <c r="N192"/>
       <c r="O192" t="s">
         <v>433</v>
       </c>
@@ -14722,9 +14334,7 @@
       <c r="M193">
         <v>1</v>
       </c>
-      <c r="N193">
-        <v>0</v>
-      </c>
+      <c r="N193"/>
       <c r="O193" t="s">
         <v>435</v>
       </c>
@@ -14772,9 +14382,7 @@
       <c r="M194">
         <v>4</v>
       </c>
-      <c r="N194">
-        <v>0</v>
-      </c>
+      <c r="N194"/>
       <c r="O194" t="s">
         <v>438</v>
       </c>
@@ -14822,9 +14430,7 @@
       <c r="M195">
         <v>5</v>
       </c>
-      <c r="N195">
-        <v>0</v>
-      </c>
+      <c r="N195"/>
       <c r="O195" t="s">
         <v>440</v>
       </c>
@@ -14872,9 +14478,7 @@
       <c r="M196">
         <v>1</v>
       </c>
-      <c r="N196">
-        <v>0</v>
-      </c>
+      <c r="N196"/>
       <c r="O196" t="s">
         <v>442</v>
       </c>
@@ -14922,9 +14526,7 @@
       <c r="M197">
         <v>4</v>
       </c>
-      <c r="N197">
-        <v>0</v>
-      </c>
+      <c r="N197"/>
       <c r="O197" t="s">
         <v>444</v>
       </c>
@@ -14972,9 +14574,7 @@
       <c r="M198">
         <v>1</v>
       </c>
-      <c r="N198">
-        <v>0</v>
-      </c>
+      <c r="N198"/>
       <c r="O198" t="s">
         <v>446</v>
       </c>
@@ -15022,9 +14622,7 @@
       <c r="M199">
         <v>1</v>
       </c>
-      <c r="N199">
-        <v>0</v>
-      </c>
+      <c r="N199"/>
       <c r="O199" t="s">
         <v>448</v>
       </c>
@@ -15072,9 +14670,7 @@
       <c r="M200">
         <v>1</v>
       </c>
-      <c r="N200">
-        <v>0</v>
-      </c>
+      <c r="N200"/>
       <c r="O200" t="s">
         <v>450</v>
       </c>
@@ -15122,9 +14718,7 @@
       <c r="M201">
         <v>23</v>
       </c>
-      <c r="N201">
-        <v>0</v>
-      </c>
+      <c r="N201"/>
       <c r="O201" t="s">
         <v>452</v>
       </c>
@@ -15172,9 +14766,7 @@
       <c r="M202">
         <v>1</v>
       </c>
-      <c r="N202">
-        <v>0</v>
-      </c>
+      <c r="N202"/>
       <c r="O202" t="s">
         <v>454</v>
       </c>
@@ -15222,9 +14814,7 @@
       <c r="M203">
         <v>13</v>
       </c>
-      <c r="N203">
-        <v>0</v>
-      </c>
+      <c r="N203"/>
       <c r="O203" t="s">
         <v>456</v>
       </c>
@@ -15272,9 +14862,7 @@
       <c r="M204">
         <v>1</v>
       </c>
-      <c r="N204">
-        <v>0</v>
-      </c>
+      <c r="N204"/>
       <c r="O204" t="s">
         <v>458</v>
       </c>
@@ -15322,9 +14910,7 @@
       <c r="M205">
         <v>1</v>
       </c>
-      <c r="N205">
-        <v>0</v>
-      </c>
+      <c r="N205"/>
       <c r="O205" t="s">
         <v>460</v>
       </c>
@@ -15372,9 +14958,7 @@
       <c r="M206">
         <v>2</v>
       </c>
-      <c r="N206">
-        <v>0</v>
-      </c>
+      <c r="N206"/>
       <c r="O206" t="s">
         <v>462</v>
       </c>
@@ -15422,9 +15006,7 @@
       <c r="M207">
         <v>2</v>
       </c>
-      <c r="N207">
-        <v>0</v>
-      </c>
+      <c r="N207"/>
       <c r="O207" t="s">
         <v>464</v>
       </c>
@@ -15472,9 +15054,7 @@
       <c r="M208">
         <v>4</v>
       </c>
-      <c r="N208">
-        <v>0</v>
-      </c>
+      <c r="N208"/>
       <c r="O208" t="s">
         <v>467</v>
       </c>
@@ -15522,9 +15102,7 @@
       <c r="M209">
         <v>2</v>
       </c>
-      <c r="N209">
-        <v>0</v>
-      </c>
+      <c r="N209"/>
       <c r="O209" t="s">
         <v>469</v>
       </c>
@@ -15572,9 +15150,7 @@
       <c r="M210">
         <v>1</v>
       </c>
-      <c r="N210">
-        <v>0</v>
-      </c>
+      <c r="N210"/>
       <c r="O210" t="s">
         <v>471</v>
       </c>
@@ -15622,9 +15198,7 @@
       <c r="M211">
         <v>1</v>
       </c>
-      <c r="N211">
-        <v>0</v>
-      </c>
+      <c r="N211"/>
       <c r="O211" t="s">
         <v>472</v>
       </c>
@@ -15672,9 +15246,7 @@
       <c r="M212">
         <v>2</v>
       </c>
-      <c r="N212">
-        <v>0</v>
-      </c>
+      <c r="N212"/>
       <c r="O212" t="s">
         <v>474</v>
       </c>
@@ -15722,9 +15294,7 @@
       <c r="M213">
         <v>1</v>
       </c>
-      <c r="N213">
-        <v>0</v>
-      </c>
+      <c r="N213"/>
       <c r="O213" t="s">
         <v>476</v>
       </c>
@@ -15772,9 +15342,7 @@
       <c r="M214">
         <v>1</v>
       </c>
-      <c r="N214">
-        <v>0</v>
-      </c>
+      <c r="N214"/>
       <c r="O214" t="s">
         <v>478</v>
       </c>
@@ -15822,9 +15390,7 @@
       <c r="M215">
         <v>3</v>
       </c>
-      <c r="N215">
-        <v>0</v>
-      </c>
+      <c r="N215"/>
       <c r="O215" t="s">
         <v>479</v>
       </c>
@@ -15872,9 +15438,7 @@
       <c r="M216">
         <v>1</v>
       </c>
-      <c r="N216">
-        <v>0</v>
-      </c>
+      <c r="N216"/>
       <c r="O216" t="s">
         <v>480</v>
       </c>
@@ -15922,9 +15486,7 @@
       <c r="M217">
         <v>1</v>
       </c>
-      <c r="N217">
-        <v>0</v>
-      </c>
+      <c r="N217"/>
       <c r="O217" t="s">
         <v>482</v>
       </c>
@@ -15972,9 +15534,7 @@
       <c r="M218">
         <v>2</v>
       </c>
-      <c r="N218">
-        <v>0</v>
-      </c>
+      <c r="N218"/>
       <c r="O218" t="s">
         <v>484</v>
       </c>
@@ -16022,9 +15582,7 @@
       <c r="M219">
         <v>2</v>
       </c>
-      <c r="N219">
-        <v>0</v>
-      </c>
+      <c r="N219"/>
       <c r="O219" t="s">
         <v>486</v>
       </c>
@@ -16072,9 +15630,7 @@
       <c r="M220">
         <v>3</v>
       </c>
-      <c r="N220">
-        <v>0</v>
-      </c>
+      <c r="N220"/>
       <c r="O220" t="s">
         <v>488</v>
       </c>
@@ -16122,9 +15678,7 @@
       <c r="M221">
         <v>6</v>
       </c>
-      <c r="N221">
-        <v>0</v>
-      </c>
+      <c r="N221"/>
       <c r="O221" t="s">
         <v>489</v>
       </c>
@@ -16172,9 +15726,7 @@
       <c r="M222">
         <v>3</v>
       </c>
-      <c r="N222">
-        <v>0</v>
-      </c>
+      <c r="N222"/>
       <c r="O222" t="s">
         <v>491</v>
       </c>
@@ -16222,9 +15774,7 @@
       <c r="M223">
         <v>2</v>
       </c>
-      <c r="N223">
-        <v>0</v>
-      </c>
+      <c r="N223"/>
       <c r="O223" t="s">
         <v>493</v>
       </c>
@@ -16272,9 +15822,7 @@
       <c r="M224">
         <v>1</v>
       </c>
-      <c r="N224">
-        <v>0</v>
-      </c>
+      <c r="N224"/>
       <c r="O224" t="s">
         <v>495</v>
       </c>
@@ -16322,9 +15870,7 @@
       <c r="M225">
         <v>1</v>
       </c>
-      <c r="N225">
-        <v>0</v>
-      </c>
+      <c r="N225"/>
       <c r="O225" t="s">
         <v>497</v>
       </c>
@@ -16372,9 +15918,7 @@
       <c r="M226">
         <v>1</v>
       </c>
-      <c r="N226">
-        <v>0</v>
-      </c>
+      <c r="N226"/>
       <c r="O226" t="s">
         <v>499</v>
       </c>
@@ -16422,9 +15966,7 @@
       <c r="M227">
         <v>2</v>
       </c>
-      <c r="N227">
-        <v>0</v>
-      </c>
+      <c r="N227"/>
       <c r="O227" t="s">
         <v>501</v>
       </c>
@@ -16472,9 +16014,7 @@
       <c r="M228">
         <v>2</v>
       </c>
-      <c r="N228">
-        <v>0</v>
-      </c>
+      <c r="N228"/>
       <c r="O228" t="s">
         <v>503</v>
       </c>
@@ -16522,9 +16062,7 @@
       <c r="M229">
         <v>1</v>
       </c>
-      <c r="N229">
-        <v>0</v>
-      </c>
+      <c r="N229"/>
       <c r="O229" t="s">
         <v>505</v>
       </c>
@@ -16572,9 +16110,7 @@
       <c r="M230">
         <v>1</v>
       </c>
-      <c r="N230">
-        <v>0</v>
-      </c>
+      <c r="N230"/>
       <c r="O230" t="s">
         <v>507</v>
       </c>
@@ -16622,9 +16158,7 @@
       <c r="M231">
         <v>2</v>
       </c>
-      <c r="N231">
-        <v>0</v>
-      </c>
+      <c r="N231"/>
       <c r="O231" t="s">
         <v>509</v>
       </c>
@@ -16672,9 +16206,7 @@
       <c r="M232">
         <v>1</v>
       </c>
-      <c r="N232">
-        <v>0</v>
-      </c>
+      <c r="N232"/>
       <c r="O232" t="s">
         <v>511</v>
       </c>
@@ -16722,9 +16254,7 @@
       <c r="M233">
         <v>1</v>
       </c>
-      <c r="N233">
-        <v>0</v>
-      </c>
+      <c r="N233"/>
       <c r="O233" t="s">
         <v>512</v>
       </c>
@@ -16772,9 +16302,7 @@
       <c r="M234">
         <v>1</v>
       </c>
-      <c r="N234">
-        <v>0</v>
-      </c>
+      <c r="N234"/>
       <c r="O234" t="s">
         <v>513</v>
       </c>
@@ -16822,9 +16350,7 @@
       <c r="M235">
         <v>1</v>
       </c>
-      <c r="N235">
-        <v>0</v>
-      </c>
+      <c r="N235"/>
       <c r="O235" t="s">
         <v>514</v>
       </c>
@@ -16872,9 +16398,7 @@
       <c r="M236">
         <v>1</v>
       </c>
-      <c r="N236">
-        <v>0</v>
-      </c>
+      <c r="N236"/>
       <c r="O236" t="s">
         <v>516</v>
       </c>
@@ -16922,9 +16446,7 @@
       <c r="M237">
         <v>1</v>
       </c>
-      <c r="N237">
-        <v>0</v>
-      </c>
+      <c r="N237"/>
       <c r="O237" t="s">
         <v>517</v>
       </c>
@@ -16972,9 +16494,7 @@
       <c r="M238">
         <v>2</v>
       </c>
-      <c r="N238">
-        <v>0</v>
-      </c>
+      <c r="N238"/>
       <c r="O238" t="s">
         <v>519</v>
       </c>
@@ -17022,9 +16542,7 @@
       <c r="M239">
         <v>2</v>
       </c>
-      <c r="N239">
-        <v>0</v>
-      </c>
+      <c r="N239"/>
       <c r="O239" t="s">
         <v>521</v>
       </c>
@@ -17072,9 +16590,7 @@
       <c r="M240">
         <v>1</v>
       </c>
-      <c r="N240">
-        <v>0</v>
-      </c>
+      <c r="N240"/>
       <c r="O240" t="s">
         <v>523</v>
       </c>
@@ -17122,9 +16638,7 @@
       <c r="M241">
         <v>3</v>
       </c>
-      <c r="N241">
-        <v>0</v>
-      </c>
+      <c r="N241"/>
       <c r="O241" t="s">
         <v>525</v>
       </c>
@@ -17172,9 +16686,7 @@
       <c r="M242">
         <v>1</v>
       </c>
-      <c r="N242">
-        <v>0</v>
-      </c>
+      <c r="N242"/>
       <c r="O242" t="s">
         <v>527</v>
       </c>
@@ -17222,9 +16734,7 @@
       <c r="M243">
         <v>1</v>
       </c>
-      <c r="N243">
-        <v>0</v>
-      </c>
+      <c r="N243"/>
       <c r="O243" t="s">
         <v>529</v>
       </c>
@@ -17272,9 +16782,7 @@
       <c r="M244">
         <v>2</v>
       </c>
-      <c r="N244">
-        <v>0</v>
-      </c>
+      <c r="N244"/>
       <c r="O244" t="s">
         <v>531</v>
       </c>
@@ -17322,9 +16830,7 @@
       <c r="M245">
         <v>1</v>
       </c>
-      <c r="N245">
-        <v>0</v>
-      </c>
+      <c r="N245"/>
       <c r="O245" t="s">
         <v>533</v>
       </c>
@@ -17372,9 +16878,7 @@
       <c r="M246">
         <v>2</v>
       </c>
-      <c r="N246">
-        <v>0</v>
-      </c>
+      <c r="N246"/>
       <c r="O246" t="s">
         <v>535</v>
       </c>
@@ -17422,9 +16926,7 @@
       <c r="M247">
         <v>2</v>
       </c>
-      <c r="N247">
-        <v>0</v>
-      </c>
+      <c r="N247"/>
       <c r="O247" t="s">
         <v>537</v>
       </c>
@@ -17472,9 +16974,7 @@
       <c r="M248">
         <v>2</v>
       </c>
-      <c r="N248">
-        <v>0</v>
-      </c>
+      <c r="N248"/>
       <c r="O248" t="s">
         <v>539</v>
       </c>
@@ -17522,9 +17022,7 @@
       <c r="M249">
         <v>2</v>
       </c>
-      <c r="N249">
-        <v>0</v>
-      </c>
+      <c r="N249"/>
       <c r="O249" t="s">
         <v>541</v>
       </c>
@@ -17572,9 +17070,7 @@
       <c r="M250">
         <v>3</v>
       </c>
-      <c r="N250">
-        <v>0</v>
-      </c>
+      <c r="N250"/>
       <c r="O250" t="s">
         <v>543</v>
       </c>
@@ -17622,9 +17118,7 @@
       <c r="M251">
         <v>1</v>
       </c>
-      <c r="N251">
-        <v>0</v>
-      </c>
+      <c r="N251"/>
       <c r="O251" t="s">
         <v>545</v>
       </c>
@@ -17672,9 +17166,7 @@
       <c r="M252">
         <v>3</v>
       </c>
-      <c r="N252">
-        <v>0</v>
-      </c>
+      <c r="N252"/>
       <c r="O252" t="s">
         <v>547</v>
       </c>
@@ -17722,9 +17214,7 @@
       <c r="M253">
         <v>1</v>
       </c>
-      <c r="N253">
-        <v>0</v>
-      </c>
+      <c r="N253"/>
       <c r="O253" t="s">
         <v>549</v>
       </c>
@@ -17772,9 +17262,7 @@
       <c r="M254">
         <v>4</v>
       </c>
-      <c r="N254">
-        <v>0</v>
-      </c>
+      <c r="N254"/>
       <c r="O254" t="s">
         <v>551</v>
       </c>
@@ -17822,9 +17310,7 @@
       <c r="M255">
         <v>1</v>
       </c>
-      <c r="N255">
-        <v>0</v>
-      </c>
+      <c r="N255"/>
       <c r="O255" t="s">
         <v>553</v>
       </c>
@@ -17872,9 +17358,7 @@
       <c r="M256">
         <v>2</v>
       </c>
-      <c r="N256">
-        <v>0</v>
-      </c>
+      <c r="N256"/>
       <c r="O256" t="s">
         <v>555</v>
       </c>
@@ -17922,9 +17406,7 @@
       <c r="M257">
         <v>6</v>
       </c>
-      <c r="N257">
-        <v>0</v>
-      </c>
+      <c r="N257"/>
       <c r="O257" t="s">
         <v>557</v>
       </c>
@@ -17972,9 +17454,7 @@
       <c r="M258">
         <v>4</v>
       </c>
-      <c r="N258">
-        <v>0</v>
-      </c>
+      <c r="N258"/>
       <c r="O258" t="s">
         <v>560</v>
       </c>
@@ -18022,9 +17502,7 @@
       <c r="M259">
         <v>1</v>
       </c>
-      <c r="N259">
-        <v>0</v>
-      </c>
+      <c r="N259"/>
       <c r="O259" t="s">
         <v>562</v>
       </c>
@@ -18072,9 +17550,7 @@
       <c r="M260">
         <v>1</v>
       </c>
-      <c r="N260">
-        <v>0</v>
-      </c>
+      <c r="N260"/>
       <c r="O260" t="s">
         <v>564</v>
       </c>
@@ -18122,9 +17598,7 @@
       <c r="M261">
         <v>3</v>
       </c>
-      <c r="N261">
-        <v>0</v>
-      </c>
+      <c r="N261"/>
       <c r="O261" t="s">
         <v>565</v>
       </c>
@@ -18172,9 +17646,7 @@
       <c r="M262">
         <v>1</v>
       </c>
-      <c r="N262">
-        <v>0</v>
-      </c>
+      <c r="N262"/>
       <c r="O262" t="s">
         <v>567</v>
       </c>
@@ -18222,9 +17694,7 @@
       <c r="M263">
         <v>1</v>
       </c>
-      <c r="N263">
-        <v>0</v>
-      </c>
+      <c r="N263"/>
       <c r="O263" t="s">
         <v>569</v>
       </c>
@@ -18272,9 +17742,7 @@
       <c r="M264">
         <v>1</v>
       </c>
-      <c r="N264">
-        <v>0</v>
-      </c>
+      <c r="N264"/>
       <c r="O264" t="s">
         <v>571</v>
       </c>
@@ -18322,9 +17790,7 @@
       <c r="M265">
         <v>8</v>
       </c>
-      <c r="N265">
-        <v>0</v>
-      </c>
+      <c r="N265"/>
       <c r="O265" t="s">
         <v>574</v>
       </c>
@@ -18372,9 +17838,7 @@
       <c r="M266">
         <v>2</v>
       </c>
-      <c r="N266">
-        <v>0</v>
-      </c>
+      <c r="N266"/>
       <c r="O266" t="s">
         <v>576</v>
       </c>
@@ -18422,9 +17886,7 @@
       <c r="M267">
         <v>2</v>
       </c>
-      <c r="N267">
-        <v>0</v>
-      </c>
+      <c r="N267"/>
       <c r="O267" t="s">
         <v>578</v>
       </c>
@@ -18472,9 +17934,7 @@
       <c r="M268">
         <v>1</v>
       </c>
-      <c r="N268">
-        <v>0</v>
-      </c>
+      <c r="N268"/>
       <c r="O268" t="s">
         <v>580</v>
       </c>
@@ -18522,9 +17982,7 @@
       <c r="M269">
         <v>2</v>
       </c>
-      <c r="N269">
-        <v>0</v>
-      </c>
+      <c r="N269"/>
       <c r="O269" t="s">
         <v>582</v>
       </c>
@@ -18572,9 +18030,7 @@
       <c r="M270">
         <v>1</v>
       </c>
-      <c r="N270">
-        <v>0</v>
-      </c>
+      <c r="N270"/>
       <c r="O270" t="s">
         <v>585</v>
       </c>
@@ -18622,9 +18078,7 @@
       <c r="M271">
         <v>3</v>
       </c>
-      <c r="N271">
-        <v>0</v>
-      </c>
+      <c r="N271"/>
       <c r="O271" t="s">
         <v>587</v>
       </c>
@@ -18672,9 +18126,7 @@
       <c r="M272">
         <v>1</v>
       </c>
-      <c r="N272">
-        <v>0</v>
-      </c>
+      <c r="N272"/>
       <c r="O272" t="s">
         <v>589</v>
       </c>
@@ -18722,9 +18174,7 @@
       <c r="M273">
         <v>8</v>
       </c>
-      <c r="N273">
-        <v>0</v>
-      </c>
+      <c r="N273"/>
       <c r="O273" t="s">
         <v>593</v>
       </c>
@@ -18772,9 +18222,7 @@
       <c r="M274">
         <v>1</v>
       </c>
-      <c r="N274">
-        <v>0</v>
-      </c>
+      <c r="N274"/>
       <c r="O274" t="s">
         <v>595</v>
       </c>
@@ -18822,9 +18270,7 @@
       <c r="M275">
         <v>2</v>
       </c>
-      <c r="N275">
-        <v>0</v>
-      </c>
+      <c r="N275"/>
       <c r="O275" t="s">
         <v>597</v>
       </c>
@@ -18872,9 +18318,7 @@
       <c r="M276">
         <v>1</v>
       </c>
-      <c r="N276">
-        <v>0</v>
-      </c>
+      <c r="N276"/>
       <c r="O276" t="s">
         <v>598</v>
       </c>
@@ -18922,9 +18366,7 @@
       <c r="M277">
         <v>1</v>
       </c>
-      <c r="N277">
-        <v>0</v>
-      </c>
+      <c r="N277"/>
       <c r="O277" t="s">
         <v>600</v>
       </c>
@@ -18972,9 +18414,7 @@
       <c r="M278">
         <v>1</v>
       </c>
-      <c r="N278">
-        <v>0</v>
-      </c>
+      <c r="N278"/>
       <c r="O278" t="s">
         <v>602</v>
       </c>
@@ -19022,9 +18462,7 @@
       <c r="M279">
         <v>1</v>
       </c>
-      <c r="N279">
-        <v>0</v>
-      </c>
+      <c r="N279"/>
       <c r="O279" t="s">
         <v>604</v>
       </c>
@@ -19072,9 +18510,7 @@
       <c r="M280">
         <v>2</v>
       </c>
-      <c r="N280">
-        <v>0</v>
-      </c>
+      <c r="N280"/>
       <c r="O280" t="s">
         <v>606</v>
       </c>
@@ -19122,9 +18558,7 @@
       <c r="M281">
         <v>1</v>
       </c>
-      <c r="N281">
-        <v>0</v>
-      </c>
+      <c r="N281"/>
       <c r="O281" t="s">
         <v>608</v>
       </c>
@@ -19172,9 +18606,7 @@
       <c r="M282">
         <v>2</v>
       </c>
-      <c r="N282">
-        <v>0</v>
-      </c>
+      <c r="N282"/>
       <c r="O282" t="s">
         <v>610</v>
       </c>
@@ -19222,9 +18654,7 @@
       <c r="M283">
         <v>1</v>
       </c>
-      <c r="N283">
-        <v>0</v>
-      </c>
+      <c r="N283"/>
       <c r="O283" t="s">
         <v>611</v>
       </c>
@@ -19272,9 +18702,7 @@
       <c r="M284">
         <v>2</v>
       </c>
-      <c r="N284">
-        <v>0</v>
-      </c>
+      <c r="N284"/>
       <c r="O284" t="s">
         <v>613</v>
       </c>
@@ -19322,9 +18750,7 @@
       <c r="M285">
         <v>1</v>
       </c>
-      <c r="N285">
-        <v>0</v>
-      </c>
+      <c r="N285"/>
       <c r="O285" t="s">
         <v>615</v>
       </c>
@@ -19372,9 +18798,7 @@
       <c r="M286">
         <v>1</v>
       </c>
-      <c r="N286">
-        <v>0</v>
-      </c>
+      <c r="N286"/>
       <c r="O286" t="s">
         <v>618</v>
       </c>
@@ -19422,9 +18846,7 @@
       <c r="M287">
         <v>2</v>
       </c>
-      <c r="N287">
-        <v>0</v>
-      </c>
+      <c r="N287"/>
       <c r="O287" t="s">
         <v>620</v>
       </c>
@@ -19472,9 +18894,7 @@
       <c r="M288">
         <v>1</v>
       </c>
-      <c r="N288">
-        <v>0</v>
-      </c>
+      <c r="N288"/>
       <c r="O288" t="s">
         <v>622</v>
       </c>
@@ -19522,9 +18942,7 @@
       <c r="M289">
         <v>3</v>
       </c>
-      <c r="N289">
-        <v>0</v>
-      </c>
+      <c r="N289"/>
       <c r="O289" t="s">
         <v>624</v>
       </c>
@@ -19572,9 +18990,7 @@
       <c r="M290">
         <v>45</v>
       </c>
-      <c r="N290">
-        <v>0</v>
-      </c>
+      <c r="N290"/>
       <c r="O290" t="s">
         <v>627</v>
       </c>
@@ -19622,9 +19038,7 @@
       <c r="M291">
         <v>5</v>
       </c>
-      <c r="N291">
-        <v>0</v>
-      </c>
+      <c r="N291"/>
       <c r="O291" t="s">
         <v>629</v>
       </c>
@@ -19672,9 +19086,7 @@
       <c r="M292">
         <v>3</v>
       </c>
-      <c r="N292">
-        <v>0</v>
-      </c>
+      <c r="N292"/>
       <c r="O292" t="s">
         <v>631</v>
       </c>
@@ -19722,9 +19134,7 @@
       <c r="M293">
         <v>1</v>
       </c>
-      <c r="N293">
-        <v>0</v>
-      </c>
+      <c r="N293"/>
       <c r="O293" t="s">
         <v>633</v>
       </c>
@@ -19772,9 +19182,7 @@
       <c r="M294">
         <v>1</v>
       </c>
-      <c r="N294">
-        <v>0</v>
-      </c>
+      <c r="N294"/>
       <c r="O294" t="s">
         <v>635</v>
       </c>
@@ -19822,9 +19230,7 @@
       <c r="M295">
         <v>3</v>
       </c>
-      <c r="N295">
-        <v>0</v>
-      </c>
+      <c r="N295"/>
       <c r="O295" t="s">
         <v>637</v>
       </c>
@@ -19872,9 +19278,7 @@
       <c r="M296">
         <v>2</v>
       </c>
-      <c r="N296">
-        <v>0</v>
-      </c>
+      <c r="N296"/>
       <c r="O296" t="s">
         <v>639</v>
       </c>
@@ -19922,9 +19326,7 @@
       <c r="M297">
         <v>1</v>
       </c>
-      <c r="N297">
-        <v>0</v>
-      </c>
+      <c r="N297"/>
       <c r="O297" t="s">
         <v>640</v>
       </c>
@@ -19972,9 +19374,7 @@
       <c r="M298">
         <v>8</v>
       </c>
-      <c r="N298">
-        <v>0</v>
-      </c>
+      <c r="N298"/>
       <c r="O298" t="s">
         <v>643</v>
       </c>
@@ -20022,9 +19422,7 @@
       <c r="M299">
         <v>1</v>
       </c>
-      <c r="N299">
-        <v>0</v>
-      </c>
+      <c r="N299"/>
       <c r="O299" t="s">
         <v>645</v>
       </c>
@@ -20072,9 +19470,7 @@
       <c r="M300">
         <v>6</v>
       </c>
-      <c r="N300">
-        <v>0</v>
-      </c>
+      <c r="N300"/>
       <c r="O300" t="s">
         <v>647</v>
       </c>
@@ -20122,9 +19518,7 @@
       <c r="M301">
         <v>4</v>
       </c>
-      <c r="N301">
-        <v>0</v>
-      </c>
+      <c r="N301"/>
       <c r="O301" t="s">
         <v>649</v>
       </c>
@@ -20172,9 +19566,7 @@
       <c r="M302">
         <v>1</v>
       </c>
-      <c r="N302">
-        <v>0</v>
-      </c>
+      <c r="N302"/>
       <c r="O302" t="s">
         <v>651</v>
       </c>
@@ -20222,9 +19614,7 @@
       <c r="M303">
         <v>1</v>
       </c>
-      <c r="N303">
-        <v>0</v>
-      </c>
+      <c r="N303"/>
       <c r="O303" t="s">
         <v>653</v>
       </c>
@@ -20272,9 +19662,7 @@
       <c r="M304">
         <v>5</v>
       </c>
-      <c r="N304">
-        <v>0</v>
-      </c>
+      <c r="N304"/>
       <c r="O304" t="s">
         <v>656</v>
       </c>
@@ -20322,9 +19710,7 @@
       <c r="M305">
         <v>2</v>
       </c>
-      <c r="N305">
-        <v>0</v>
-      </c>
+      <c r="N305"/>
       <c r="O305" t="s">
         <v>658</v>
       </c>
@@ -20372,9 +19758,7 @@
       <c r="M306">
         <v>3</v>
       </c>
-      <c r="N306">
-        <v>0</v>
-      </c>
+      <c r="N306"/>
       <c r="O306" t="s">
         <v>660</v>
       </c>
@@ -20422,9 +19806,7 @@
       <c r="M307">
         <v>3</v>
       </c>
-      <c r="N307">
-        <v>0</v>
-      </c>
+      <c r="N307"/>
       <c r="O307" t="s">
         <v>661</v>
       </c>
@@ -20472,9 +19854,7 @@
       <c r="M308">
         <v>2</v>
       </c>
-      <c r="N308">
-        <v>0</v>
-      </c>
+      <c r="N308"/>
       <c r="O308" t="s">
         <v>663</v>
       </c>
@@ -20522,9 +19902,7 @@
       <c r="M309">
         <v>1</v>
       </c>
-      <c r="N309">
-        <v>0</v>
-      </c>
+      <c r="N309"/>
       <c r="O309" t="s">
         <v>665</v>
       </c>
@@ -20572,9 +19950,7 @@
       <c r="M310">
         <v>1</v>
       </c>
-      <c r="N310">
-        <v>0</v>
-      </c>
+      <c r="N310"/>
       <c r="O310" t="s">
         <v>668</v>
       </c>
@@ -20622,9 +19998,7 @@
       <c r="M311">
         <v>1</v>
       </c>
-      <c r="N311">
-        <v>0</v>
-      </c>
+      <c r="N311"/>
       <c r="O311" t="s">
         <v>670</v>
       </c>
@@ -20672,9 +20046,7 @@
       <c r="M312">
         <v>2</v>
       </c>
-      <c r="N312">
-        <v>0</v>
-      </c>
+      <c r="N312"/>
       <c r="O312" t="s">
         <v>672</v>
       </c>
@@ -20722,9 +20094,7 @@
       <c r="M313">
         <v>1</v>
       </c>
-      <c r="N313">
-        <v>0</v>
-      </c>
+      <c r="N313"/>
       <c r="O313" t="s">
         <v>674</v>
       </c>
@@ -20772,9 +20142,7 @@
       <c r="M314">
         <v>4</v>
       </c>
-      <c r="N314">
-        <v>0</v>
-      </c>
+      <c r="N314"/>
       <c r="O314" t="s">
         <v>676</v>
       </c>
@@ -20822,9 +20190,7 @@
       <c r="M315">
         <v>2</v>
       </c>
-      <c r="N315">
-        <v>0</v>
-      </c>
+      <c r="N315"/>
       <c r="O315" t="s">
         <v>678</v>
       </c>
@@ -20872,9 +20238,7 @@
       <c r="M316">
         <v>1</v>
       </c>
-      <c r="N316">
-        <v>0</v>
-      </c>
+      <c r="N316"/>
       <c r="O316" t="s">
         <v>680</v>
       </c>
@@ -20922,9 +20286,7 @@
       <c r="M317">
         <v>1</v>
       </c>
-      <c r="N317">
-        <v>0</v>
-      </c>
+      <c r="N317"/>
       <c r="O317" t="s">
         <v>681</v>
       </c>
@@ -20972,9 +20334,7 @@
       <c r="M318">
         <v>1</v>
       </c>
-      <c r="N318">
-        <v>0</v>
-      </c>
+      <c r="N318"/>
       <c r="O318" t="s">
         <v>683</v>
       </c>
@@ -21022,9 +20382,7 @@
       <c r="M319">
         <v>1</v>
       </c>
-      <c r="N319">
-        <v>0</v>
-      </c>
+      <c r="N319"/>
       <c r="O319" t="s">
         <v>685</v>
       </c>
@@ -21072,9 +20430,7 @@
       <c r="M320">
         <v>1</v>
       </c>
-      <c r="N320">
-        <v>0</v>
-      </c>
+      <c r="N320"/>
       <c r="O320" t="s">
         <v>687</v>
       </c>
@@ -21122,9 +20478,7 @@
       <c r="M321">
         <v>1</v>
       </c>
-      <c r="N321">
-        <v>0</v>
-      </c>
+      <c r="N321"/>
       <c r="O321" t="s">
         <v>689</v>
       </c>
@@ -21172,9 +20526,7 @@
       <c r="M322">
         <v>1</v>
       </c>
-      <c r="N322">
-        <v>0</v>
-      </c>
+      <c r="N322"/>
       <c r="O322" t="s">
         <v>691</v>
       </c>
@@ -21222,9 +20574,7 @@
       <c r="M323">
         <v>1</v>
       </c>
-      <c r="N323">
-        <v>0</v>
-      </c>
+      <c r="N323"/>
       <c r="O323" t="s">
         <v>692</v>
       </c>
@@ -21272,9 +20622,7 @@
       <c r="M324">
         <v>1</v>
       </c>
-      <c r="N324">
-        <v>0</v>
-      </c>
+      <c r="N324"/>
       <c r="O324" t="s">
         <v>693</v>
       </c>
@@ -21322,9 +20670,7 @@
       <c r="M325">
         <v>1</v>
       </c>
-      <c r="N325">
-        <v>0</v>
-      </c>
+      <c r="N325"/>
       <c r="O325" t="s">
         <v>695</v>
       </c>
@@ -21372,9 +20718,7 @@
       <c r="M326">
         <v>1</v>
       </c>
-      <c r="N326">
-        <v>0</v>
-      </c>
+      <c r="N326"/>
       <c r="O326" t="s">
         <v>697</v>
       </c>
@@ -21422,9 +20766,7 @@
       <c r="M327">
         <v>1</v>
       </c>
-      <c r="N327">
-        <v>0</v>
-      </c>
+      <c r="N327"/>
       <c r="O327" t="s">
         <v>699</v>
       </c>
@@ -21472,9 +20814,7 @@
       <c r="M328">
         <v>1</v>
       </c>
-      <c r="N328">
-        <v>0</v>
-      </c>
+      <c r="N328"/>
       <c r="O328" t="s">
         <v>701</v>
       </c>
@@ -21522,9 +20862,7 @@
       <c r="M329">
         <v>1</v>
       </c>
-      <c r="N329">
-        <v>0</v>
-      </c>
+      <c r="N329"/>
       <c r="O329" t="s">
         <v>702</v>
       </c>
@@ -21572,9 +20910,7 @@
       <c r="M330">
         <v>1</v>
       </c>
-      <c r="N330">
-        <v>0</v>
-      </c>
+      <c r="N330"/>
       <c r="O330" t="s">
         <v>703</v>
       </c>
@@ -21622,9 +20958,7 @@
       <c r="M331">
         <v>1</v>
       </c>
-      <c r="N331">
-        <v>0</v>
-      </c>
+      <c r="N331"/>
       <c r="O331" t="s">
         <v>705</v>
       </c>
@@ -21672,9 +21006,7 @@
       <c r="M332">
         <v>2</v>
       </c>
-      <c r="N332">
-        <v>0</v>
-      </c>
+      <c r="N332"/>
       <c r="O332" t="s">
         <v>707</v>
       </c>
@@ -21722,9 +21054,7 @@
       <c r="M333">
         <v>1</v>
       </c>
-      <c r="N333">
-        <v>0</v>
-      </c>
+      <c r="N333"/>
       <c r="O333" t="s">
         <v>709</v>
       </c>
@@ -21772,9 +21102,7 @@
       <c r="M334">
         <v>1</v>
       </c>
-      <c r="N334">
-        <v>0</v>
-      </c>
+      <c r="N334"/>
       <c r="O334" t="s">
         <v>711</v>
       </c>
@@ -21822,9 +21150,7 @@
       <c r="M335">
         <v>1</v>
       </c>
-      <c r="N335">
-        <v>0</v>
-      </c>
+      <c r="N335"/>
       <c r="O335" t="s">
         <v>713</v>
       </c>
@@ -21872,9 +21198,7 @@
       <c r="M336">
         <v>1</v>
       </c>
-      <c r="N336">
-        <v>0</v>
-      </c>
+      <c r="N336"/>
       <c r="O336" t="s">
         <v>715</v>
       </c>
@@ -21922,9 +21246,7 @@
       <c r="M337">
         <v>1</v>
       </c>
-      <c r="N337">
-        <v>0</v>
-      </c>
+      <c r="N337"/>
       <c r="O337" t="s">
         <v>717</v>
       </c>
@@ -21972,9 +21294,7 @@
       <c r="M338">
         <v>2</v>
       </c>
-      <c r="N338">
-        <v>0</v>
-      </c>
+      <c r="N338"/>
       <c r="O338" t="s">
         <v>719</v>
       </c>
@@ -22022,9 +21342,7 @@
       <c r="M339">
         <v>1</v>
       </c>
-      <c r="N339">
-        <v>0</v>
-      </c>
+      <c r="N339"/>
       <c r="O339" t="s">
         <v>721</v>
       </c>
@@ -22072,9 +21390,7 @@
       <c r="M340">
         <v>2</v>
       </c>
-      <c r="N340">
-        <v>0</v>
-      </c>
+      <c r="N340"/>
       <c r="O340" t="s">
         <v>723</v>
       </c>
@@ -22122,9 +21438,7 @@
       <c r="M341">
         <v>1</v>
       </c>
-      <c r="N341">
-        <v>0</v>
-      </c>
+      <c r="N341"/>
       <c r="O341" t="s">
         <v>725</v>
       </c>
@@ -22172,9 +21486,7 @@
       <c r="M342">
         <v>1</v>
       </c>
-      <c r="N342">
-        <v>0</v>
-      </c>
+      <c r="N342"/>
       <c r="O342" t="s">
         <v>727</v>
       </c>
@@ -22222,9 +21534,7 @@
       <c r="M343">
         <v>2</v>
       </c>
-      <c r="N343">
-        <v>0</v>
-      </c>
+      <c r="N343"/>
       <c r="O343" t="s">
         <v>729</v>
       </c>
@@ -22272,9 +21582,7 @@
       <c r="M344">
         <v>1</v>
       </c>
-      <c r="N344">
-        <v>0</v>
-      </c>
+      <c r="N344"/>
       <c r="O344" t="s">
         <v>731</v>
       </c>
@@ -22322,9 +21630,7 @@
       <c r="M345">
         <v>1</v>
       </c>
-      <c r="N345">
-        <v>0</v>
-      </c>
+      <c r="N345"/>
       <c r="O345" t="s">
         <v>733</v>
       </c>
@@ -22372,9 +21678,7 @@
       <c r="M346">
         <v>1</v>
       </c>
-      <c r="N346">
-        <v>0</v>
-      </c>
+      <c r="N346"/>
       <c r="O346" t="s">
         <v>735</v>
       </c>
@@ -22422,9 +21726,7 @@
       <c r="M347">
         <v>1</v>
       </c>
-      <c r="N347">
-        <v>0</v>
-      </c>
+      <c r="N347"/>
       <c r="O347" t="s">
         <v>737</v>
       </c>
@@ -22472,9 +21774,7 @@
       <c r="M348">
         <v>1</v>
       </c>
-      <c r="N348">
-        <v>0</v>
-      </c>
+      <c r="N348"/>
       <c r="O348" t="s">
         <v>739</v>
       </c>
@@ -22522,9 +21822,7 @@
       <c r="M349">
         <v>1</v>
       </c>
-      <c r="N349">
-        <v>0</v>
-      </c>
+      <c r="N349"/>
       <c r="O349" t="s">
         <v>741</v>
       </c>
@@ -22572,9 +21870,7 @@
       <c r="M350">
         <v>1</v>
       </c>
-      <c r="N350">
-        <v>0</v>
-      </c>
+      <c r="N350"/>
       <c r="O350" t="s">
         <v>743</v>
       </c>
@@ -22622,9 +21918,7 @@
       <c r="M351">
         <v>1</v>
       </c>
-      <c r="N351">
-        <v>0</v>
-      </c>
+      <c r="N351"/>
       <c r="O351" t="s">
         <v>745</v>
       </c>
@@ -22672,9 +21966,7 @@
       <c r="M352">
         <v>1</v>
       </c>
-      <c r="N352">
-        <v>0</v>
-      </c>
+      <c r="N352"/>
       <c r="O352" t="s">
         <v>747</v>
       </c>
@@ -22722,9 +22014,7 @@
       <c r="M353">
         <v>1</v>
       </c>
-      <c r="N353">
-        <v>0</v>
-      </c>
+      <c r="N353"/>
       <c r="O353" t="s">
         <v>749</v>
       </c>
@@ -22772,9 +22062,7 @@
       <c r="M354">
         <v>1</v>
       </c>
-      <c r="N354">
-        <v>0</v>
-      </c>
+      <c r="N354"/>
       <c r="O354" t="s">
         <v>751</v>
       </c>
@@ -22822,9 +22110,7 @@
       <c r="M355">
         <v>3</v>
       </c>
-      <c r="N355">
-        <v>0</v>
-      </c>
+      <c r="N355"/>
       <c r="O355" t="s">
         <v>752</v>
       </c>
@@ -22872,9 +22158,7 @@
       <c r="M356">
         <v>1</v>
       </c>
-      <c r="N356">
-        <v>0</v>
-      </c>
+      <c r="N356"/>
       <c r="O356" t="s">
         <v>754</v>
       </c>
@@ -22922,9 +22206,7 @@
       <c r="M357">
         <v>1</v>
       </c>
-      <c r="N357">
-        <v>0</v>
-      </c>
+      <c r="N357"/>
       <c r="O357" t="s">
         <v>755</v>
       </c>
@@ -22972,9 +22254,7 @@
       <c r="M358">
         <v>1</v>
       </c>
-      <c r="N358">
-        <v>0</v>
-      </c>
+      <c r="N358"/>
       <c r="O358" t="s">
         <v>757</v>
       </c>
@@ -23022,9 +22302,7 @@
       <c r="M359">
         <v>1</v>
       </c>
-      <c r="N359">
-        <v>0</v>
-      </c>
+      <c r="N359"/>
       <c r="O359" t="s">
         <v>758</v>
       </c>
@@ -23072,9 +22350,7 @@
       <c r="M360">
         <v>1</v>
       </c>
-      <c r="N360">
-        <v>0</v>
-      </c>
+      <c r="N360"/>
       <c r="O360" t="s">
         <v>760</v>
       </c>
@@ -23122,9 +22398,7 @@
       <c r="M361">
         <v>1</v>
       </c>
-      <c r="N361">
-        <v>0</v>
-      </c>
+      <c r="N361"/>
       <c r="O361" t="s">
         <v>762</v>
       </c>
@@ -23172,9 +22446,7 @@
       <c r="M362">
         <v>1</v>
       </c>
-      <c r="N362">
-        <v>0</v>
-      </c>
+      <c r="N362"/>
       <c r="O362" t="s">
         <v>764</v>
       </c>
@@ -23222,9 +22494,7 @@
       <c r="M363">
         <v>1</v>
       </c>
-      <c r="N363">
-        <v>0</v>
-      </c>
+      <c r="N363"/>
       <c r="O363" t="s">
         <v>766</v>
       </c>
@@ -23272,9 +22542,7 @@
       <c r="M364">
         <v>2</v>
       </c>
-      <c r="N364">
-        <v>0</v>
-      </c>
+      <c r="N364"/>
       <c r="O364" t="s">
         <v>768</v>
       </c>
@@ -23322,9 +22590,7 @@
       <c r="M365">
         <v>2</v>
       </c>
-      <c r="N365">
-        <v>0</v>
-      </c>
+      <c r="N365"/>
       <c r="O365" t="s">
         <v>770</v>
       </c>
@@ -23372,9 +22638,7 @@
       <c r="M366">
         <v>1</v>
       </c>
-      <c r="N366">
-        <v>0</v>
-      </c>
+      <c r="N366"/>
       <c r="O366" t="s">
         <v>772</v>
       </c>
@@ -23422,9 +22686,7 @@
       <c r="M367">
         <v>2</v>
       </c>
-      <c r="N367">
-        <v>0</v>
-      </c>
+      <c r="N367"/>
       <c r="O367" t="s">
         <v>775</v>
       </c>
@@ -23472,9 +22734,7 @@
       <c r="M368">
         <v>1</v>
       </c>
-      <c r="N368">
-        <v>0</v>
-      </c>
+      <c r="N368"/>
       <c r="O368" t="s">
         <v>777</v>
       </c>
@@ -23522,9 +22782,7 @@
       <c r="M369">
         <v>1</v>
       </c>
-      <c r="N369">
-        <v>0</v>
-      </c>
+      <c r="N369"/>
       <c r="O369" t="s">
         <v>779</v>
       </c>
@@ -23572,9 +22830,7 @@
       <c r="M370">
         <v>1</v>
       </c>
-      <c r="N370">
-        <v>0</v>
-      </c>
+      <c r="N370"/>
       <c r="O370" t="s">
         <v>781</v>
       </c>
@@ -23622,9 +22878,7 @@
       <c r="M371">
         <v>2</v>
       </c>
-      <c r="N371">
-        <v>0</v>
-      </c>
+      <c r="N371"/>
       <c r="O371" t="s">
         <v>783</v>
       </c>
@@ -23672,9 +22926,7 @@
       <c r="M372">
         <v>1</v>
       </c>
-      <c r="N372">
-        <v>0</v>
-      </c>
+      <c r="N372"/>
       <c r="O372" t="s">
         <v>786</v>
       </c>
@@ -23722,9 +22974,7 @@
       <c r="M373">
         <v>1</v>
       </c>
-      <c r="N373">
-        <v>0</v>
-      </c>
+      <c r="N373"/>
       <c r="O373" t="s">
         <v>788</v>
       </c>
@@ -23772,9 +23022,7 @@
       <c r="M374">
         <v>3</v>
       </c>
-      <c r="N374">
-        <v>0</v>
-      </c>
+      <c r="N374"/>
       <c r="O374" t="s">
         <v>790</v>
       </c>
@@ -23822,9 +23070,7 @@
       <c r="M375">
         <v>4</v>
       </c>
-      <c r="N375">
-        <v>0</v>
-      </c>
+      <c r="N375"/>
       <c r="O375" t="s">
         <v>793</v>
       </c>
@@ -23872,9 +23118,7 @@
       <c r="M376">
         <v>2</v>
       </c>
-      <c r="N376">
-        <v>0</v>
-      </c>
+      <c r="N376"/>
       <c r="O376" t="s">
         <v>795</v>
       </c>
@@ -23922,9 +23166,7 @@
       <c r="M377">
         <v>2</v>
       </c>
-      <c r="N377">
-        <v>0</v>
-      </c>
+      <c r="N377"/>
       <c r="O377" t="s">
         <v>796</v>
       </c>
@@ -23972,9 +23214,7 @@
       <c r="M378">
         <v>1</v>
       </c>
-      <c r="N378">
-        <v>0</v>
-      </c>
+      <c r="N378"/>
       <c r="O378" t="s">
         <v>799</v>
       </c>
@@ -24022,9 +23262,7 @@
       <c r="M379">
         <v>1</v>
       </c>
-      <c r="N379">
-        <v>0</v>
-      </c>
+      <c r="N379"/>
       <c r="O379" t="s">
         <v>802</v>
       </c>
@@ -24072,9 +23310,7 @@
       <c r="M380">
         <v>2</v>
       </c>
-      <c r="N380">
-        <v>0</v>
-      </c>
+      <c r="N380"/>
       <c r="O380" t="s">
         <v>805</v>
       </c>
@@ -24122,9 +23358,7 @@
       <c r="M381">
         <v>1</v>
       </c>
-      <c r="N381">
-        <v>0</v>
-      </c>
+      <c r="N381"/>
       <c r="O381" t="s">
         <v>807</v>
       </c>
@@ -24172,9 +23406,7 @@
       <c r="M382">
         <v>3</v>
       </c>
-      <c r="N382">
-        <v>0</v>
-      </c>
+      <c r="N382"/>
       <c r="O382" t="s">
         <v>809</v>
       </c>
@@ -24222,9 +23454,7 @@
       <c r="M383">
         <v>1</v>
       </c>
-      <c r="N383">
-        <v>0</v>
-      </c>
+      <c r="N383"/>
       <c r="O383" t="s">
         <v>811</v>
       </c>
@@ -24272,9 +23502,7 @@
       <c r="M384">
         <v>1</v>
       </c>
-      <c r="N384">
-        <v>0</v>
-      </c>
+      <c r="N384"/>
       <c r="O384" t="s">
         <v>813</v>
       </c>
@@ -24322,9 +23550,7 @@
       <c r="M385">
         <v>2</v>
       </c>
-      <c r="N385">
-        <v>0</v>
-      </c>
+      <c r="N385"/>
       <c r="O385" t="s">
         <v>815</v>
       </c>
@@ -24372,9 +23598,7 @@
       <c r="M386">
         <v>1</v>
       </c>
-      <c r="N386">
-        <v>0</v>
-      </c>
+      <c r="N386"/>
       <c r="O386" t="s">
         <v>817</v>
       </c>
@@ -24422,9 +23646,7 @@
       <c r="M387">
         <v>1</v>
       </c>
-      <c r="N387">
-        <v>0</v>
-      </c>
+      <c r="N387"/>
       <c r="O387" t="s">
         <v>819</v>
       </c>
@@ -24472,9 +23694,7 @@
       <c r="M388">
         <v>1</v>
       </c>
-      <c r="N388">
-        <v>0</v>
-      </c>
+      <c r="N388"/>
       <c r="O388" t="s">
         <v>821</v>
       </c>
@@ -24522,9 +23742,7 @@
       <c r="M389">
         <v>1</v>
       </c>
-      <c r="N389">
-        <v>0</v>
-      </c>
+      <c r="N389"/>
       <c r="O389" t="s">
         <v>823</v>
       </c>
@@ -24572,9 +23790,7 @@
       <c r="M390">
         <v>2</v>
       </c>
-      <c r="N390">
-        <v>0</v>
-      </c>
+      <c r="N390"/>
       <c r="O390" t="s">
         <v>825</v>
       </c>
@@ -24622,9 +23838,7 @@
       <c r="M391">
         <v>1</v>
       </c>
-      <c r="N391">
-        <v>0</v>
-      </c>
+      <c r="N391"/>
       <c r="O391" t="s">
         <v>827</v>
       </c>
@@ -24672,9 +23886,7 @@
       <c r="M392">
         <v>1</v>
       </c>
-      <c r="N392">
-        <v>0</v>
-      </c>
+      <c r="N392"/>
       <c r="O392" t="s">
         <v>828</v>
       </c>
@@ -24722,9 +23934,7 @@
       <c r="M393">
         <v>2</v>
       </c>
-      <c r="N393">
-        <v>0</v>
-      </c>
+      <c r="N393"/>
       <c r="O393" t="s">
         <v>830</v>
       </c>
@@ -24772,9 +23982,7 @@
       <c r="M394">
         <v>2</v>
       </c>
-      <c r="N394">
-        <v>0</v>
-      </c>
+      <c r="N394"/>
       <c r="O394" t="s">
         <v>832</v>
       </c>
@@ -24822,9 +24030,7 @@
       <c r="M395">
         <v>3</v>
       </c>
-      <c r="N395">
-        <v>0</v>
-      </c>
+      <c r="N395"/>
       <c r="O395" t="s">
         <v>834</v>
       </c>
@@ -24872,9 +24078,7 @@
       <c r="M396">
         <v>1</v>
       </c>
-      <c r="N396">
-        <v>0</v>
-      </c>
+      <c r="N396"/>
       <c r="O396" t="s">
         <v>836</v>
       </c>
@@ -24922,9 +24126,7 @@
       <c r="M397">
         <v>1</v>
       </c>
-      <c r="N397">
-        <v>0</v>
-      </c>
+      <c r="N397"/>
       <c r="O397" t="s">
         <v>838</v>
       </c>
@@ -24972,9 +24174,7 @@
       <c r="M398">
         <v>1</v>
       </c>
-      <c r="N398">
-        <v>0</v>
-      </c>
+      <c r="N398"/>
       <c r="O398" t="s">
         <v>840</v>
       </c>
@@ -25022,9 +24222,7 @@
       <c r="M399">
         <v>1</v>
       </c>
-      <c r="N399">
-        <v>0</v>
-      </c>
+      <c r="N399"/>
       <c r="O399" t="s">
         <v>842</v>
       </c>
@@ -25072,9 +24270,7 @@
       <c r="M400">
         <v>1</v>
       </c>
-      <c r="N400">
-        <v>0</v>
-      </c>
+      <c r="N400"/>
       <c r="O400" t="s">
         <v>844</v>
       </c>
@@ -25122,9 +24318,7 @@
       <c r="M401">
         <v>1</v>
       </c>
-      <c r="N401">
-        <v>0</v>
-      </c>
+      <c r="N401"/>
       <c r="O401" t="s">
         <v>846</v>
       </c>
@@ -25172,9 +24366,7 @@
       <c r="M402">
         <v>2</v>
       </c>
-      <c r="N402">
-        <v>0</v>
-      </c>
+      <c r="N402"/>
       <c r="O402" t="s">
         <v>848</v>
       </c>
@@ -25222,9 +24414,7 @@
       <c r="M403">
         <v>3</v>
       </c>
-      <c r="N403">
-        <v>0</v>
-      </c>
+      <c r="N403"/>
       <c r="O403" t="s">
         <v>851</v>
       </c>
@@ -25272,9 +24462,7 @@
       <c r="M404">
         <v>2</v>
       </c>
-      <c r="N404">
-        <v>0</v>
-      </c>
+      <c r="N404"/>
       <c r="O404" t="s">
         <v>853</v>
       </c>
@@ -25322,9 +24510,7 @@
       <c r="M405">
         <v>2</v>
       </c>
-      <c r="N405">
-        <v>0</v>
-      </c>
+      <c r="N405"/>
       <c r="O405" t="s">
         <v>855</v>
       </c>
@@ -25372,9 +24558,7 @@
       <c r="M406">
         <v>6</v>
       </c>
-      <c r="N406">
-        <v>0</v>
-      </c>
+      <c r="N406"/>
       <c r="O406" t="s">
         <v>857</v>
       </c>
@@ -25422,9 +24606,7 @@
       <c r="M407">
         <v>3</v>
       </c>
-      <c r="N407">
-        <v>0</v>
-      </c>
+      <c r="N407"/>
       <c r="O407" t="s">
         <v>859</v>
       </c>
@@ -25472,9 +24654,7 @@
       <c r="M408">
         <v>5</v>
       </c>
-      <c r="N408">
-        <v>0</v>
-      </c>
+      <c r="N408"/>
       <c r="O408" t="s">
         <v>861</v>
       </c>
@@ -25522,9 +24702,7 @@
       <c r="M409">
         <v>2</v>
       </c>
-      <c r="N409">
-        <v>0</v>
-      </c>
+      <c r="N409"/>
       <c r="O409" t="s">
         <v>863</v>
       </c>
@@ -25572,9 +24750,7 @@
       <c r="M410">
         <v>3</v>
       </c>
-      <c r="N410">
-        <v>0</v>
-      </c>
+      <c r="N410"/>
       <c r="O410" t="s">
         <v>865</v>
       </c>
@@ -25622,9 +24798,7 @@
       <c r="M411">
         <v>1</v>
       </c>
-      <c r="N411">
-        <v>0</v>
-      </c>
+      <c r="N411"/>
       <c r="O411" t="s">
         <v>867</v>
       </c>
@@ -25672,9 +24846,7 @@
       <c r="M412">
         <v>2</v>
       </c>
-      <c r="N412">
-        <v>0</v>
-      </c>
+      <c r="N412"/>
       <c r="O412" t="s">
         <v>869</v>
       </c>
@@ -25722,9 +24894,7 @@
       <c r="M413">
         <v>1</v>
       </c>
-      <c r="N413">
-        <v>0</v>
-      </c>
+      <c r="N413"/>
       <c r="O413" t="s">
         <v>871</v>
       </c>
@@ -25772,9 +24942,7 @@
       <c r="M414">
         <v>1</v>
       </c>
-      <c r="N414">
-        <v>0</v>
-      </c>
+      <c r="N414"/>
       <c r="O414" t="s">
         <v>873</v>
       </c>
@@ -25822,9 +24990,7 @@
       <c r="M415">
         <v>2</v>
       </c>
-      <c r="N415">
-        <v>0</v>
-      </c>
+      <c r="N415"/>
       <c r="O415" t="s">
         <v>875</v>
       </c>
@@ -25872,9 +25038,7 @@
       <c r="M416">
         <v>1</v>
       </c>
-      <c r="N416">
-        <v>0</v>
-      </c>
+      <c r="N416"/>
       <c r="O416" t="s">
         <v>877</v>
       </c>
@@ -25922,9 +25086,7 @@
       <c r="M417">
         <v>2</v>
       </c>
-      <c r="N417">
-        <v>0</v>
-      </c>
+      <c r="N417"/>
       <c r="O417" t="s">
         <v>879</v>
       </c>
@@ -25972,9 +25134,7 @@
       <c r="M418">
         <v>1</v>
       </c>
-      <c r="N418">
-        <v>0</v>
-      </c>
+      <c r="N418"/>
       <c r="O418" t="s">
         <v>881</v>
       </c>
@@ -26022,9 +25182,7 @@
       <c r="M419">
         <v>2</v>
       </c>
-      <c r="N419">
-        <v>0</v>
-      </c>
+      <c r="N419"/>
       <c r="O419" t="s">
         <v>883</v>
       </c>
@@ -26072,9 +25230,7 @@
       <c r="M420">
         <v>1</v>
       </c>
-      <c r="N420">
-        <v>0</v>
-      </c>
+      <c r="N420"/>
       <c r="O420" t="s">
         <v>885</v>
       </c>
@@ -26122,9 +25278,7 @@
       <c r="M421">
         <v>2</v>
       </c>
-      <c r="N421">
-        <v>0</v>
-      </c>
+      <c r="N421"/>
       <c r="O421" t="s">
         <v>887</v>
       </c>
@@ -26172,9 +25326,7 @@
       <c r="M422">
         <v>1</v>
       </c>
-      <c r="N422">
-        <v>0</v>
-      </c>
+      <c r="N422"/>
       <c r="O422" t="s">
         <v>889</v>
       </c>
@@ -26222,9 +25374,7 @@
       <c r="M423">
         <v>2</v>
       </c>
-      <c r="N423">
-        <v>0</v>
-      </c>
+      <c r="N423"/>
       <c r="O423" t="s">
         <v>891</v>
       </c>
@@ -26272,9 +25422,7 @@
       <c r="M424">
         <v>2</v>
       </c>
-      <c r="N424">
-        <v>0</v>
-      </c>
+      <c r="N424"/>
       <c r="O424" t="s">
         <v>893</v>
       </c>
@@ -26322,9 +25470,7 @@
       <c r="M425">
         <v>1</v>
       </c>
-      <c r="N425">
-        <v>0</v>
-      </c>
+      <c r="N425"/>
       <c r="O425" t="s">
         <v>895</v>
       </c>
@@ -26372,9 +25518,7 @@
       <c r="M426">
         <v>1</v>
       </c>
-      <c r="N426">
-        <v>0</v>
-      </c>
+      <c r="N426"/>
       <c r="O426" t="s">
         <v>897</v>
       </c>
@@ -26422,9 +25566,7 @@
       <c r="M427">
         <v>1</v>
       </c>
-      <c r="N427">
-        <v>0</v>
-      </c>
+      <c r="N427"/>
       <c r="O427" t="s">
         <v>899</v>
       </c>
@@ -26472,9 +25614,7 @@
       <c r="M428">
         <v>1</v>
       </c>
-      <c r="N428">
-        <v>0</v>
-      </c>
+      <c r="N428"/>
       <c r="O428" t="s">
         <v>901</v>
       </c>
@@ -26522,9 +25662,7 @@
       <c r="M429">
         <v>1</v>
       </c>
-      <c r="N429">
-        <v>0</v>
-      </c>
+      <c r="N429"/>
       <c r="O429" t="s">
         <v>903</v>
       </c>
@@ -26572,9 +25710,7 @@
       <c r="M430">
         <v>1</v>
       </c>
-      <c r="N430">
-        <v>0</v>
-      </c>
+      <c r="N430"/>
       <c r="O430" t="s">
         <v>905</v>
       </c>
@@ -26622,9 +25758,7 @@
       <c r="M431">
         <v>2</v>
       </c>
-      <c r="N431">
-        <v>0</v>
-      </c>
+      <c r="N431"/>
       <c r="O431" t="s">
         <v>907</v>
       </c>
@@ -26672,9 +25806,7 @@
       <c r="M432">
         <v>1</v>
       </c>
-      <c r="N432">
-        <v>0</v>
-      </c>
+      <c r="N432"/>
       <c r="O432" t="s">
         <v>909</v>
       </c>
@@ -26722,9 +25854,7 @@
       <c r="M433">
         <v>5</v>
       </c>
-      <c r="N433">
-        <v>0</v>
-      </c>
+      <c r="N433"/>
       <c r="O433" t="s">
         <v>911</v>
       </c>
@@ -26772,9 +25902,7 @@
       <c r="M434">
         <v>1</v>
       </c>
-      <c r="N434">
-        <v>0</v>
-      </c>
+      <c r="N434"/>
       <c r="O434" t="s">
         <v>913</v>
       </c>
@@ -26822,9 +25950,7 @@
       <c r="M435">
         <v>1</v>
       </c>
-      <c r="N435">
-        <v>0</v>
-      </c>
+      <c r="N435"/>
       <c r="O435" t="s">
         <v>915</v>
       </c>
@@ -26872,9 +25998,7 @@
       <c r="M436">
         <v>2</v>
       </c>
-      <c r="N436">
-        <v>0</v>
-      </c>
+      <c r="N436"/>
       <c r="O436" t="s">
         <v>917</v>
       </c>
@@ -26922,9 +26046,7 @@
       <c r="M437">
         <v>5</v>
       </c>
-      <c r="N437">
-        <v>0</v>
-      </c>
+      <c r="N437"/>
       <c r="O437" t="s">
         <v>920</v>
       </c>
@@ -26972,9 +26094,7 @@
       <c r="M438">
         <v>3</v>
       </c>
-      <c r="N438">
-        <v>0</v>
-      </c>
+      <c r="N438"/>
       <c r="O438" t="s">
         <v>922</v>
       </c>
@@ -27022,9 +26142,7 @@
       <c r="M439">
         <v>7</v>
       </c>
-      <c r="N439">
-        <v>0</v>
-      </c>
+      <c r="N439"/>
       <c r="O439" t="s">
         <v>924</v>
       </c>
@@ -27072,9 +26190,7 @@
       <c r="M440">
         <v>1</v>
       </c>
-      <c r="N440">
-        <v>0</v>
-      </c>
+      <c r="N440"/>
       <c r="O440" t="s">
         <v>926</v>
       </c>
@@ -27122,9 +26238,7 @@
       <c r="M441">
         <v>2</v>
       </c>
-      <c r="N441">
-        <v>0</v>
-      </c>
+      <c r="N441"/>
       <c r="O441" t="s">
         <v>928</v>
       </c>
@@ -27172,9 +26286,7 @@
       <c r="M442">
         <v>2</v>
       </c>
-      <c r="N442">
-        <v>0</v>
-      </c>
+      <c r="N442"/>
       <c r="O442" t="s">
         <v>930</v>
       </c>
@@ -27222,9 +26334,7 @@
       <c r="M443">
         <v>1</v>
       </c>
-      <c r="N443">
-        <v>0</v>
-      </c>
+      <c r="N443"/>
       <c r="O443" t="s">
         <v>932</v>
       </c>
@@ -27272,9 +26382,7 @@
       <c r="M444">
         <v>1</v>
       </c>
-      <c r="N444">
-        <v>0</v>
-      </c>
+      <c r="N444"/>
       <c r="O444" t="s">
         <v>934</v>
       </c>
@@ -27322,9 +26430,7 @@
       <c r="M445">
         <v>1</v>
       </c>
-      <c r="N445">
-        <v>0</v>
-      </c>
+      <c r="N445"/>
       <c r="O445" t="s">
         <v>935</v>
       </c>
@@ -27372,9 +26478,7 @@
       <c r="M446">
         <v>1</v>
       </c>
-      <c r="N446">
-        <v>0</v>
-      </c>
+      <c r="N446"/>
       <c r="O446" t="s">
         <v>937</v>
       </c>
@@ -27422,9 +26526,7 @@
       <c r="M447">
         <v>1</v>
       </c>
-      <c r="N447">
-        <v>0</v>
-      </c>
+      <c r="N447"/>
       <c r="O447" t="s">
         <v>939</v>
       </c>
@@ -27472,9 +26574,7 @@
       <c r="M448">
         <v>1</v>
       </c>
-      <c r="N448">
-        <v>0</v>
-      </c>
+      <c r="N448"/>
       <c r="O448" t="s">
         <v>941</v>
       </c>
@@ -27522,9 +26622,7 @@
       <c r="M449">
         <v>1</v>
       </c>
-      <c r="N449">
-        <v>0</v>
-      </c>
+      <c r="N449"/>
       <c r="O449" t="s">
         <v>943</v>
       </c>
@@ -27572,9 +26670,7 @@
       <c r="M450">
         <v>1</v>
       </c>
-      <c r="N450">
-        <v>0</v>
-      </c>
+      <c r="N450"/>
       <c r="O450" t="s">
         <v>945</v>
       </c>
@@ -27622,9 +26718,7 @@
       <c r="M451">
         <v>1</v>
       </c>
-      <c r="N451">
-        <v>0</v>
-      </c>
+      <c r="N451"/>
       <c r="O451" t="s">
         <v>947</v>
       </c>
@@ -27672,9 +26766,7 @@
       <c r="M452">
         <v>1</v>
       </c>
-      <c r="N452">
-        <v>0</v>
-      </c>
+      <c r="N452"/>
       <c r="O452" t="s">
         <v>949</v>
       </c>
@@ -27722,9 +26814,7 @@
       <c r="M453">
         <v>1</v>
       </c>
-      <c r="N453">
-        <v>0</v>
-      </c>
+      <c r="N453"/>
       <c r="O453" t="s">
         <v>951</v>
       </c>
@@ -27772,9 +26862,7 @@
       <c r="M454">
         <v>1</v>
       </c>
-      <c r="N454">
-        <v>0</v>
-      </c>
+      <c r="N454"/>
       <c r="O454" t="s">
         <v>953</v>
       </c>
@@ -27822,9 +26910,7 @@
       <c r="M455">
         <v>1</v>
       </c>
-      <c r="N455">
-        <v>0</v>
-      </c>
+      <c r="N455"/>
       <c r="O455" t="s">
         <v>955</v>
       </c>
@@ -27872,9 +26958,7 @@
       <c r="M456">
         <v>1</v>
       </c>
-      <c r="N456">
-        <v>0</v>
-      </c>
+      <c r="N456"/>
       <c r="O456" t="s">
         <v>957</v>
       </c>
@@ -27922,9 +27006,7 @@
       <c r="M457">
         <v>1</v>
       </c>
-      <c r="N457">
-        <v>0</v>
-      </c>
+      <c r="N457"/>
       <c r="O457" t="s">
         <v>959</v>
       </c>
@@ -27972,9 +27054,7 @@
       <c r="M458">
         <v>1</v>
       </c>
-      <c r="N458">
-        <v>0</v>
-      </c>
+      <c r="N458"/>
       <c r="O458" t="s">
         <v>961</v>
       </c>
@@ -28022,9 +27102,7 @@
       <c r="M459">
         <v>1</v>
       </c>
-      <c r="N459">
-        <v>0</v>
-      </c>
+      <c r="N459"/>
       <c r="O459" t="s">
         <v>963</v>
       </c>
@@ -28072,9 +27150,7 @@
       <c r="M460">
         <v>8</v>
       </c>
-      <c r="N460">
-        <v>0</v>
-      </c>
+      <c r="N460"/>
       <c r="O460" t="s">
         <v>966</v>
       </c>
@@ -28122,9 +27198,7 @@
       <c r="M461">
         <v>2</v>
       </c>
-      <c r="N461">
-        <v>0</v>
-      </c>
+      <c r="N461"/>
       <c r="O461" t="s">
         <v>968</v>
       </c>
@@ -28172,9 +27246,7 @@
       <c r="M462">
         <v>3</v>
       </c>
-      <c r="N462">
-        <v>0</v>
-      </c>
+      <c r="N462"/>
       <c r="O462" t="s">
         <v>971</v>
       </c>
@@ -28222,9 +27294,7 @@
       <c r="M463">
         <v>3</v>
       </c>
-      <c r="N463">
-        <v>0</v>
-      </c>
+      <c r="N463"/>
       <c r="O463" t="s">
         <v>973</v>
       </c>
@@ -28272,9 +27342,7 @@
       <c r="M464">
         <v>2</v>
       </c>
-      <c r="N464">
-        <v>0</v>
-      </c>
+      <c r="N464"/>
       <c r="O464" t="s">
         <v>975</v>
       </c>
@@ -28322,9 +27390,7 @@
       <c r="M465">
         <v>6</v>
       </c>
-      <c r="N465">
-        <v>0</v>
-      </c>
+      <c r="N465"/>
       <c r="O465" t="s">
         <v>977</v>
       </c>
@@ -28372,9 +27438,7 @@
       <c r="M466">
         <v>6</v>
       </c>
-      <c r="N466">
-        <v>0</v>
-      </c>
+      <c r="N466"/>
       <c r="O466" t="s">
         <v>978</v>
       </c>
@@ -28422,9 +27486,7 @@
       <c r="M467">
         <v>7</v>
       </c>
-      <c r="N467">
-        <v>0</v>
-      </c>
+      <c r="N467"/>
       <c r="O467" t="s">
         <v>980</v>
       </c>
@@ -28472,9 +27534,7 @@
       <c r="M468">
         <v>1</v>
       </c>
-      <c r="N468">
-        <v>0</v>
-      </c>
+      <c r="N468"/>
       <c r="O468" t="s">
         <v>982</v>
       </c>
@@ -28522,9 +27582,7 @@
       <c r="M469">
         <v>12</v>
       </c>
-      <c r="N469">
-        <v>0</v>
-      </c>
+      <c r="N469"/>
       <c r="O469" t="s">
         <v>985</v>
       </c>
@@ -28572,9 +27630,7 @@
       <c r="M470">
         <v>6</v>
       </c>
-      <c r="N470">
-        <v>0</v>
-      </c>
+      <c r="N470"/>
       <c r="O470" t="s">
         <v>987</v>
       </c>
@@ -28622,9 +27678,7 @@
       <c r="M471">
         <v>6</v>
       </c>
-      <c r="N471">
-        <v>0</v>
-      </c>
+      <c r="N471"/>
       <c r="O471" t="s">
         <v>989</v>
       </c>
@@ -28672,9 +27726,7 @@
       <c r="M472">
         <v>9</v>
       </c>
-      <c r="N472">
-        <v>0</v>
-      </c>
+      <c r="N472"/>
       <c r="O472" t="s">
         <v>991</v>
       </c>
@@ -28722,9 +27774,7 @@
       <c r="M473">
         <v>4</v>
       </c>
-      <c r="N473">
-        <v>0</v>
-      </c>
+      <c r="N473"/>
       <c r="O473" t="s">
         <v>993</v>
       </c>
@@ -28772,9 +27822,7 @@
       <c r="M474">
         <v>6</v>
       </c>
-      <c r="N474">
-        <v>0</v>
-      </c>
+      <c r="N474"/>
       <c r="O474" t="s">
         <v>995</v>
       </c>
@@ -28822,9 +27870,7 @@
       <c r="M475">
         <v>15</v>
       </c>
-      <c r="N475">
-        <v>0</v>
-      </c>
+      <c r="N475"/>
       <c r="O475" t="s">
         <v>997</v>
       </c>
@@ -28872,9 +27918,7 @@
       <c r="M476">
         <v>3</v>
       </c>
-      <c r="N476">
-        <v>0</v>
-      </c>
+      <c r="N476"/>
       <c r="O476" t="s">
         <v>999</v>
       </c>
@@ -28922,9 +27966,7 @@
       <c r="M477">
         <v>3</v>
       </c>
-      <c r="N477">
-        <v>0</v>
-      </c>
+      <c r="N477"/>
       <c r="O477" t="s">
         <v>1001</v>
       </c>
@@ -28972,9 +28014,7 @@
       <c r="M478">
         <v>6</v>
       </c>
-      <c r="N478">
-        <v>0</v>
-      </c>
+      <c r="N478"/>
       <c r="O478" t="s">
         <v>1003</v>
       </c>
@@ -29022,9 +28062,7 @@
       <c r="M479">
         <v>33</v>
       </c>
-      <c r="N479">
-        <v>0</v>
-      </c>
+      <c r="N479"/>
       <c r="O479" t="s">
         <v>1005</v>
       </c>
@@ -29072,9 +28110,7 @@
       <c r="M480">
         <v>6</v>
       </c>
-      <c r="N480">
-        <v>0</v>
-      </c>
+      <c r="N480"/>
       <c r="O480" t="s">
         <v>1007</v>
       </c>
@@ -29122,9 +28158,7 @@
       <c r="M481">
         <v>41</v>
       </c>
-      <c r="N481">
-        <v>0</v>
-      </c>
+      <c r="N481"/>
       <c r="O481" t="s">
         <v>1009</v>
       </c>
@@ -29172,9 +28206,7 @@
       <c r="M482">
         <v>7</v>
       </c>
-      <c r="N482">
-        <v>0</v>
-      </c>
+      <c r="N482"/>
       <c r="O482" t="s">
         <v>1011</v>
       </c>
@@ -29222,9 +28254,7 @@
       <c r="M483">
         <v>5</v>
       </c>
-      <c r="N483">
-        <v>0</v>
-      </c>
+      <c r="N483"/>
       <c r="O483" t="s">
         <v>1013</v>
       </c>
@@ -29272,9 +28302,7 @@
       <c r="M484">
         <v>10</v>
       </c>
-      <c r="N484">
-        <v>0</v>
-      </c>
+      <c r="N484"/>
       <c r="O484" t="s">
         <v>1015</v>
       </c>
@@ -29322,9 +28350,7 @@
       <c r="M485">
         <v>9</v>
       </c>
-      <c r="N485">
-        <v>0</v>
-      </c>
+      <c r="N485"/>
       <c r="O485" t="s">
         <v>1017</v>
       </c>
@@ -29372,9 +28398,7 @@
       <c r="M486">
         <v>5</v>
       </c>
-      <c r="N486">
-        <v>0</v>
-      </c>
+      <c r="N486"/>
       <c r="O486" t="s">
         <v>1019</v>
       </c>
@@ -29422,9 +28446,7 @@
       <c r="M487">
         <v>4</v>
       </c>
-      <c r="N487">
-        <v>0</v>
-      </c>
+      <c r="N487"/>
       <c r="O487" t="s">
         <v>1021</v>
       </c>
@@ -29472,9 +28494,7 @@
       <c r="M488">
         <v>4</v>
       </c>
-      <c r="N488">
-        <v>0</v>
-      </c>
+      <c r="N488"/>
       <c r="O488" t="s">
         <v>1023</v>
       </c>
@@ -29522,9 +28542,7 @@
       <c r="M489">
         <v>3</v>
       </c>
-      <c r="N489">
-        <v>0</v>
-      </c>
+      <c r="N489"/>
       <c r="O489" t="s">
         <v>1025</v>
       </c>
@@ -29572,9 +28590,7 @@
       <c r="M490">
         <v>2</v>
       </c>
-      <c r="N490">
-        <v>0</v>
-      </c>
+      <c r="N490"/>
       <c r="O490" t="s">
         <v>1027</v>
       </c>
@@ -29622,9 +28638,7 @@
       <c r="M491">
         <v>32</v>
       </c>
-      <c r="N491">
-        <v>0</v>
-      </c>
+      <c r="N491"/>
       <c r="O491" t="s">
         <v>1030</v>
       </c>
@@ -29672,9 +28686,7 @@
       <c r="M492">
         <v>11</v>
       </c>
-      <c r="N492">
-        <v>0</v>
-      </c>
+      <c r="N492"/>
       <c r="O492" t="s">
         <v>1032</v>
       </c>
@@ -29722,9 +28734,7 @@
       <c r="M493">
         <v>22</v>
       </c>
-      <c r="N493">
-        <v>0</v>
-      </c>
+      <c r="N493"/>
       <c r="O493" t="s">
         <v>1034</v>
       </c>
@@ -29772,9 +28782,7 @@
       <c r="M494">
         <v>13</v>
       </c>
-      <c r="N494">
-        <v>0</v>
-      </c>
+      <c r="N494"/>
       <c r="O494" t="s">
         <v>1036</v>
       </c>
@@ -29822,9 +28830,7 @@
       <c r="M495">
         <v>16</v>
       </c>
-      <c r="N495">
-        <v>0</v>
-      </c>
+      <c r="N495"/>
       <c r="O495" t="s">
         <v>1038</v>
       </c>
@@ -29872,9 +28878,7 @@
       <c r="M496">
         <v>15</v>
       </c>
-      <c r="N496">
-        <v>0</v>
-      </c>
+      <c r="N496"/>
       <c r="O496" t="s">
         <v>1041</v>
       </c>
@@ -29922,9 +28926,7 @@
       <c r="M497">
         <v>4</v>
       </c>
-      <c r="N497">
-        <v>0</v>
-      </c>
+      <c r="N497"/>
       <c r="O497" t="s">
         <v>1042</v>
       </c>
@@ -29972,9 +28974,7 @@
       <c r="M498">
         <v>11</v>
       </c>
-      <c r="N498">
-        <v>0</v>
-      </c>
+      <c r="N498"/>
       <c r="O498" t="s">
         <v>1044</v>
       </c>
@@ -30022,9 +29022,7 @@
       <c r="M499">
         <v>2</v>
       </c>
-      <c r="N499">
-        <v>0</v>
-      </c>
+      <c r="N499"/>
       <c r="O499" t="s">
         <v>1045</v>
       </c>
@@ -30072,9 +29070,7 @@
       <c r="M500">
         <v>7</v>
       </c>
-      <c r="N500">
-        <v>0</v>
-      </c>
+      <c r="N500"/>
       <c r="O500" t="s">
         <v>1047</v>
       </c>
@@ -30122,9 +29118,7 @@
       <c r="M501">
         <v>3</v>
       </c>
-      <c r="N501">
-        <v>0</v>
-      </c>
+      <c r="N501"/>
       <c r="O501" t="s">
         <v>1049</v>
       </c>
@@ -30172,9 +29166,7 @@
       <c r="M502">
         <v>3</v>
       </c>
-      <c r="N502">
-        <v>0</v>
-      </c>
+      <c r="N502"/>
       <c r="O502" t="s">
         <v>1051</v>
       </c>
@@ -30222,9 +29214,7 @@
       <c r="M503">
         <v>4</v>
       </c>
-      <c r="N503">
-        <v>0</v>
-      </c>
+      <c r="N503"/>
       <c r="O503" t="s">
         <v>1054</v>
       </c>
@@ -30272,9 +29262,7 @@
       <c r="M504">
         <v>9</v>
       </c>
-      <c r="N504">
-        <v>0</v>
-      </c>
+      <c r="N504"/>
       <c r="O504" t="s">
         <v>1056</v>
       </c>
@@ -30322,9 +29310,7 @@
       <c r="M505">
         <v>4</v>
       </c>
-      <c r="N505">
-        <v>0</v>
-      </c>
+      <c r="N505"/>
       <c r="O505" t="s">
         <v>1057</v>
       </c>
@@ -30372,9 +29358,7 @@
       <c r="M506">
         <v>3</v>
       </c>
-      <c r="N506">
-        <v>0</v>
-      </c>
+      <c r="N506"/>
       <c r="O506" t="s">
         <v>1059</v>
       </c>
@@ -30422,9 +29406,7 @@
       <c r="M507">
         <v>2</v>
       </c>
-      <c r="N507">
-        <v>0</v>
-      </c>
+      <c r="N507"/>
       <c r="O507" t="s">
         <v>1060</v>
       </c>
@@ -30472,9 +29454,7 @@
       <c r="M508">
         <v>1</v>
       </c>
-      <c r="N508">
-        <v>0</v>
-      </c>
+      <c r="N508"/>
       <c r="O508" t="s">
         <v>1061</v>
       </c>
@@ -30522,9 +29502,7 @@
       <c r="M509">
         <v>1</v>
       </c>
-      <c r="N509">
-        <v>0</v>
-      </c>
+      <c r="N509"/>
       <c r="O509" t="s">
         <v>1063</v>
       </c>
@@ -30572,9 +29550,7 @@
       <c r="M510">
         <v>1</v>
       </c>
-      <c r="N510">
-        <v>0</v>
-      </c>
+      <c r="N510"/>
       <c r="O510" t="s">
         <v>1065</v>
       </c>
@@ -30622,9 +29598,7 @@
       <c r="M511">
         <v>2</v>
       </c>
-      <c r="N511">
-        <v>0</v>
-      </c>
+      <c r="N511"/>
       <c r="O511" t="s">
         <v>1067</v>
       </c>
@@ -30672,9 +29646,7 @@
       <c r="M512">
         <v>6</v>
       </c>
-      <c r="N512">
-        <v>0</v>
-      </c>
+      <c r="N512"/>
       <c r="O512" t="s">
         <v>1070</v>
       </c>
@@ -30722,9 +29694,7 @@
       <c r="M513">
         <v>6</v>
       </c>
-      <c r="N513">
-        <v>0</v>
-      </c>
+      <c r="N513"/>
       <c r="O513" t="s">
         <v>1072</v>
       </c>
@@ -30772,9 +29742,7 @@
       <c r="M514">
         <v>4</v>
       </c>
-      <c r="N514">
-        <v>0</v>
-      </c>
+      <c r="N514"/>
       <c r="O514" t="s">
         <v>1074</v>
       </c>
@@ -30822,9 +29790,7 @@
       <c r="M515">
         <v>4</v>
       </c>
-      <c r="N515">
-        <v>0</v>
-      </c>
+      <c r="N515"/>
       <c r="O515" t="s">
         <v>1076</v>
       </c>
@@ -30872,9 +29838,7 @@
       <c r="M516">
         <v>6</v>
       </c>
-      <c r="N516">
-        <v>0</v>
-      </c>
+      <c r="N516"/>
       <c r="O516" t="s">
         <v>1078</v>
       </c>
@@ -30922,9 +29886,7 @@
       <c r="M517">
         <v>3</v>
       </c>
-      <c r="N517">
-        <v>0</v>
-      </c>
+      <c r="N517"/>
       <c r="O517" t="s">
         <v>1080</v>
       </c>
@@ -30972,9 +29934,7 @@
       <c r="M518">
         <v>2</v>
       </c>
-      <c r="N518">
-        <v>0</v>
-      </c>
+      <c r="N518"/>
       <c r="O518" t="s">
         <v>1082</v>
       </c>
@@ -31022,9 +29982,7 @@
       <c r="M519">
         <v>1</v>
       </c>
-      <c r="N519">
-        <v>0</v>
-      </c>
+      <c r="N519"/>
       <c r="O519" t="s">
         <v>1084</v>
       </c>
@@ -31072,9 +30030,7 @@
       <c r="M520">
         <v>1</v>
       </c>
-      <c r="N520">
-        <v>0</v>
-      </c>
+      <c r="N520"/>
       <c r="O520" t="s">
         <v>1086</v>
       </c>
@@ -31122,9 +30078,7 @@
       <c r="M521">
         <v>1</v>
       </c>
-      <c r="N521">
-        <v>0</v>
-      </c>
+      <c r="N521"/>
       <c r="O521" t="s">
         <v>1088</v>
       </c>
@@ -31172,9 +30126,7 @@
       <c r="M522">
         <v>1</v>
       </c>
-      <c r="N522">
-        <v>0</v>
-      </c>
+      <c r="N522"/>
       <c r="O522" t="s">
         <v>1090</v>
       </c>
@@ -31222,9 +30174,7 @@
       <c r="M523">
         <v>1</v>
       </c>
-      <c r="N523">
-        <v>0</v>
-      </c>
+      <c r="N523"/>
       <c r="O523" t="s">
         <v>1092</v>
       </c>
@@ -31272,9 +30222,7 @@
       <c r="M524">
         <v>1</v>
       </c>
-      <c r="N524">
-        <v>0</v>
-      </c>
+      <c r="N524"/>
       <c r="O524" t="s">
         <v>1094</v>
       </c>
@@ -31322,9 +30270,7 @@
       <c r="M525">
         <v>1</v>
       </c>
-      <c r="N525">
-        <v>0</v>
-      </c>
+      <c r="N525"/>
       <c r="O525" t="s">
         <v>1096</v>
       </c>
@@ -31372,9 +30318,7 @@
       <c r="M526">
         <v>1</v>
       </c>
-      <c r="N526">
-        <v>0</v>
-      </c>
+      <c r="N526"/>
       <c r="O526" t="s">
         <v>1098</v>
       </c>
@@ -31422,9 +30366,7 @@
       <c r="M527">
         <v>1</v>
       </c>
-      <c r="N527">
-        <v>0</v>
-      </c>
+      <c r="N527"/>
       <c r="O527" t="s">
         <v>1100</v>
       </c>
@@ -31472,9 +30414,7 @@
       <c r="M528">
         <v>1</v>
       </c>
-      <c r="N528">
-        <v>0</v>
-      </c>
+      <c r="N528"/>
       <c r="O528" t="s">
         <v>1102</v>
       </c>
@@ -31522,9 +30462,7 @@
       <c r="M529">
         <v>5</v>
       </c>
-      <c r="N529">
-        <v>0</v>
-      </c>
+      <c r="N529"/>
       <c r="O529" t="s">
         <v>1105</v>
       </c>
@@ -31572,9 +30510,7 @@
       <c r="M530">
         <v>20</v>
       </c>
-      <c r="N530">
-        <v>0</v>
-      </c>
+      <c r="N530"/>
       <c r="O530" t="s">
         <v>1107</v>
       </c>
@@ -31622,9 +30558,7 @@
       <c r="M531">
         <v>5</v>
       </c>
-      <c r="N531">
-        <v>0</v>
-      </c>
+      <c r="N531"/>
       <c r="O531" t="s">
         <v>1109</v>
       </c>
@@ -31672,9 +30606,7 @@
       <c r="M532">
         <v>2</v>
       </c>
-      <c r="N532">
-        <v>0</v>
-      </c>
+      <c r="N532"/>
       <c r="O532" t="s">
         <v>1111</v>
       </c>
@@ -31722,9 +30654,7 @@
       <c r="M533">
         <v>1</v>
       </c>
-      <c r="N533">
-        <v>0</v>
-      </c>
+      <c r="N533"/>
       <c r="O533" t="s">
         <v>1113</v>
       </c>
@@ -31772,9 +30702,7 @@
       <c r="M534">
         <v>2</v>
       </c>
-      <c r="N534">
-        <v>0</v>
-      </c>
+      <c r="N534"/>
       <c r="O534" t="s">
         <v>1115</v>
       </c>
@@ -31822,9 +30750,7 @@
       <c r="M535">
         <v>1</v>
       </c>
-      <c r="N535">
-        <v>0</v>
-      </c>
+      <c r="N535"/>
       <c r="O535" t="s">
         <v>1117</v>
       </c>
@@ -31872,9 +30798,7 @@
       <c r="M536">
         <v>2</v>
       </c>
-      <c r="N536">
-        <v>0</v>
-      </c>
+      <c r="N536"/>
       <c r="O536" t="s">
         <v>1119</v>
       </c>
@@ -31922,9 +30846,7 @@
       <c r="M537">
         <v>1</v>
       </c>
-      <c r="N537">
-        <v>0</v>
-      </c>
+      <c r="N537"/>
       <c r="O537" t="s">
         <v>1121</v>
       </c>
@@ -31972,9 +30894,7 @@
       <c r="M538">
         <v>1</v>
       </c>
-      <c r="N538">
-        <v>0</v>
-      </c>
+      <c r="N538"/>
       <c r="O538" t="s">
         <v>1123</v>
       </c>
@@ -32022,9 +30942,7 @@
       <c r="M539">
         <v>1</v>
       </c>
-      <c r="N539">
-        <v>0</v>
-      </c>
+      <c r="N539"/>
       <c r="O539" t="s">
         <v>1125</v>
       </c>
@@ -32072,9 +30990,7 @@
       <c r="M540">
         <v>1</v>
       </c>
-      <c r="N540">
-        <v>0</v>
-      </c>
+      <c r="N540"/>
       <c r="O540" t="s">
         <v>1127</v>
       </c>
@@ -32122,9 +31038,7 @@
       <c r="M541">
         <v>1</v>
       </c>
-      <c r="N541">
-        <v>0</v>
-      </c>
+      <c r="N541"/>
       <c r="O541" t="s">
         <v>1129</v>
       </c>
@@ -32172,9 +31086,7 @@
       <c r="M542">
         <v>1</v>
       </c>
-      <c r="N542">
-        <v>0</v>
-      </c>
+      <c r="N542"/>
       <c r="O542" t="s">
         <v>1131</v>
       </c>
@@ -32222,9 +31134,7 @@
       <c r="M543">
         <v>3</v>
       </c>
-      <c r="N543">
-        <v>0</v>
-      </c>
+      <c r="N543"/>
       <c r="O543" t="s">
         <v>1133</v>
       </c>
@@ -32272,9 +31182,7 @@
       <c r="M544">
         <v>1</v>
       </c>
-      <c r="N544">
-        <v>0</v>
-      </c>
+      <c r="N544"/>
       <c r="O544" t="s">
         <v>1135</v>
       </c>
@@ -32322,9 +31230,7 @@
       <c r="M545">
         <v>1</v>
       </c>
-      <c r="N545">
-        <v>0</v>
-      </c>
+      <c r="N545"/>
       <c r="O545" t="s">
         <v>1137</v>
       </c>
@@ -32372,9 +31278,7 @@
       <c r="M546">
         <v>1</v>
       </c>
-      <c r="N546">
-        <v>0</v>
-      </c>
+      <c r="N546"/>
       <c r="O546" t="s">
         <v>1139</v>
       </c>
@@ -32422,9 +31326,7 @@
       <c r="M547">
         <v>1</v>
       </c>
-      <c r="N547">
-        <v>0</v>
-      </c>
+      <c r="N547"/>
       <c r="O547" t="s">
         <v>1141</v>
       </c>
@@ -32472,9 +31374,7 @@
       <c r="M548">
         <v>2</v>
       </c>
-      <c r="N548">
-        <v>0</v>
-      </c>
+      <c r="N548"/>
       <c r="O548" t="s">
         <v>1143</v>
       </c>
@@ -32522,9 +31422,7 @@
       <c r="M549">
         <v>1</v>
       </c>
-      <c r="N549">
-        <v>0</v>
-      </c>
+      <c r="N549"/>
       <c r="O549" t="s">
         <v>1145</v>
       </c>
@@ -32572,9 +31470,7 @@
       <c r="M550">
         <v>1</v>
       </c>
-      <c r="N550">
-        <v>0</v>
-      </c>
+      <c r="N550"/>
       <c r="O550" t="s">
         <v>1147</v>
       </c>
@@ -32622,9 +31518,7 @@
       <c r="M551">
         <v>1</v>
       </c>
-      <c r="N551">
-        <v>0</v>
-      </c>
+      <c r="N551"/>
       <c r="O551" t="s">
         <v>1149</v>
       </c>
@@ -32672,9 +31566,7 @@
       <c r="M552">
         <v>3</v>
       </c>
-      <c r="N552">
-        <v>0</v>
-      </c>
+      <c r="N552"/>
       <c r="O552" t="s">
         <v>1151</v>
       </c>
@@ -32722,9 +31614,7 @@
       <c r="M553">
         <v>1</v>
       </c>
-      <c r="N553">
-        <v>0</v>
-      </c>
+      <c r="N553"/>
       <c r="O553" t="s">
         <v>1153</v>
       </c>
@@ -32772,9 +31662,7 @@
       <c r="M554">
         <v>4</v>
       </c>
-      <c r="N554">
-        <v>0</v>
-      </c>
+      <c r="N554"/>
       <c r="O554" t="s">
         <v>1155</v>
       </c>
@@ -32822,9 +31710,7 @@
       <c r="M555">
         <v>2</v>
       </c>
-      <c r="N555">
-        <v>0</v>
-      </c>
+      <c r="N555"/>
       <c r="O555" t="s">
         <v>1156</v>
       </c>
@@ -32872,9 +31758,7 @@
       <c r="M556">
         <v>3</v>
       </c>
-      <c r="N556">
-        <v>0</v>
-      </c>
+      <c r="N556"/>
       <c r="O556" t="s">
         <v>1158</v>
       </c>
@@ -32922,9 +31806,7 @@
       <c r="M557">
         <v>1</v>
       </c>
-      <c r="N557">
-        <v>0</v>
-      </c>
+      <c r="N557"/>
       <c r="O557" t="s">
         <v>1160</v>
       </c>
@@ -32972,9 +31854,7 @@
       <c r="M558">
         <v>1</v>
       </c>
-      <c r="N558">
-        <v>0</v>
-      </c>
+      <c r="N558"/>
       <c r="O558" t="s">
         <v>1162</v>
       </c>
@@ -33022,9 +31902,7 @@
       <c r="M559">
         <v>1</v>
       </c>
-      <c r="N559">
-        <v>0</v>
-      </c>
+      <c r="N559"/>
       <c r="O559" t="s">
         <v>1164</v>
       </c>
@@ -33072,9 +31950,7 @@
       <c r="M560">
         <v>20</v>
       </c>
-      <c r="N560">
-        <v>0</v>
-      </c>
+      <c r="N560"/>
       <c r="O560" t="s">
         <v>1167</v>
       </c>
@@ -33122,9 +31998,7 @@
       <c r="M561">
         <v>10</v>
       </c>
-      <c r="N561">
-        <v>0</v>
-      </c>
+      <c r="N561"/>
       <c r="O561" t="s">
         <v>1169</v>
       </c>
@@ -33172,9 +32046,7 @@
       <c r="M562">
         <v>13</v>
       </c>
-      <c r="N562">
-        <v>0</v>
-      </c>
+      <c r="N562"/>
       <c r="O562" t="s">
         <v>1171</v>
       </c>
@@ -33222,9 +32094,7 @@
       <c r="M563">
         <v>8</v>
       </c>
-      <c r="N563">
-        <v>0</v>
-      </c>
+      <c r="N563"/>
       <c r="O563" t="s">
         <v>1173</v>
       </c>
@@ -33272,9 +32142,7 @@
       <c r="M564">
         <v>16</v>
       </c>
-      <c r="N564">
-        <v>0</v>
-      </c>
+      <c r="N564"/>
       <c r="O564" t="s">
         <v>1176</v>
       </c>
@@ -33322,9 +32190,7 @@
       <c r="M565">
         <v>3</v>
       </c>
-      <c r="N565">
-        <v>0</v>
-      </c>
+      <c r="N565"/>
       <c r="O565" t="s">
         <v>1178</v>
       </c>
@@ -33372,9 +32238,7 @@
       <c r="M566">
         <v>1</v>
       </c>
-      <c r="N566">
-        <v>0</v>
-      </c>
+      <c r="N566"/>
       <c r="O566" t="s">
         <v>1180</v>
       </c>
@@ -33422,9 +32286,7 @@
       <c r="M567">
         <v>1</v>
       </c>
-      <c r="N567">
-        <v>0</v>
-      </c>
+      <c r="N567"/>
       <c r="O567" t="s">
         <v>1182</v>
       </c>
@@ -33472,9 +32334,7 @@
       <c r="M568">
         <v>2</v>
       </c>
-      <c r="N568">
-        <v>0</v>
-      </c>
+      <c r="N568"/>
       <c r="O568" t="s">
         <v>1186</v>
       </c>
@@ -33522,9 +32382,7 @@
       <c r="M569">
         <v>1</v>
       </c>
-      <c r="N569">
-        <v>0</v>
-      </c>
+      <c r="N569"/>
       <c r="O569" t="s">
         <v>1188</v>
       </c>
@@ -33572,9 +32430,7 @@
       <c r="M570">
         <v>2</v>
       </c>
-      <c r="N570">
-        <v>0</v>
-      </c>
+      <c r="N570"/>
       <c r="O570" t="s">
         <v>1190</v>
       </c>
@@ -33622,9 +32478,7 @@
       <c r="M571">
         <v>1</v>
       </c>
-      <c r="N571">
-        <v>0</v>
-      </c>
+      <c r="N571"/>
       <c r="O571" t="s">
         <v>1192</v>
       </c>
@@ -33672,9 +32526,7 @@
       <c r="M572">
         <v>1</v>
       </c>
-      <c r="N572">
-        <v>0</v>
-      </c>
+      <c r="N572"/>
       <c r="O572" t="s">
         <v>1193</v>
       </c>
@@ -33722,9 +32574,7 @@
       <c r="M573">
         <v>1</v>
       </c>
-      <c r="N573">
-        <v>0</v>
-      </c>
+      <c r="N573"/>
       <c r="O573" t="s">
         <v>1194</v>
       </c>
@@ -33772,9 +32622,7 @@
       <c r="M574">
         <v>2</v>
       </c>
-      <c r="N574">
-        <v>0</v>
-      </c>
+      <c r="N574"/>
       <c r="O574" t="s">
         <v>1196</v>
       </c>
@@ -33822,9 +32670,7 @@
       <c r="M575">
         <v>1</v>
       </c>
-      <c r="N575">
-        <v>0</v>
-      </c>
+      <c r="N575"/>
       <c r="O575" t="s">
         <v>1197</v>
       </c>
@@ -33872,9 +32718,7 @@
       <c r="M576">
         <v>1</v>
       </c>
-      <c r="N576">
-        <v>0</v>
-      </c>
+      <c r="N576"/>
       <c r="O576" t="s">
         <v>1198</v>
       </c>
@@ -33922,9 +32766,7 @@
       <c r="M577">
         <v>1</v>
       </c>
-      <c r="N577">
-        <v>0</v>
-      </c>
+      <c r="N577"/>
       <c r="O577" t="s">
         <v>1199</v>
       </c>
@@ -33972,9 +32814,7 @@
       <c r="M578">
         <v>1</v>
       </c>
-      <c r="N578">
-        <v>0</v>
-      </c>
+      <c r="N578"/>
       <c r="O578" t="s">
         <v>1200</v>
       </c>
@@ -34022,9 +32862,7 @@
       <c r="M579">
         <v>2</v>
       </c>
-      <c r="N579">
-        <v>0</v>
-      </c>
+      <c r="N579"/>
       <c r="O579" t="s">
         <v>1201</v>
       </c>
@@ -34072,9 +32910,7 @@
       <c r="M580">
         <v>3</v>
       </c>
-      <c r="N580">
-        <v>0</v>
-      </c>
+      <c r="N580"/>
       <c r="O580" t="s">
         <v>1204</v>
       </c>
@@ -34122,9 +32958,7 @@
       <c r="M581">
         <v>2</v>
       </c>
-      <c r="N581">
-        <v>0</v>
-      </c>
+      <c r="N581"/>
       <c r="O581" t="s">
         <v>1206</v>
       </c>
@@ -34172,9 +33006,7 @@
       <c r="M582">
         <v>1</v>
       </c>
-      <c r="N582">
-        <v>0</v>
-      </c>
+      <c r="N582"/>
       <c r="O582" t="s">
         <v>1208</v>
       </c>
@@ -34222,9 +33054,7 @@
       <c r="M583">
         <v>2</v>
       </c>
-      <c r="N583">
-        <v>0</v>
-      </c>
+      <c r="N583"/>
       <c r="O583" t="s">
         <v>1211</v>
       </c>
@@ -34272,9 +33102,7 @@
       <c r="M584">
         <v>2</v>
       </c>
-      <c r="N584">
-        <v>0</v>
-      </c>
+      <c r="N584"/>
       <c r="O584" t="s">
         <v>1213</v>
       </c>
@@ -34322,9 +33150,7 @@
       <c r="M585">
         <v>40</v>
       </c>
-      <c r="N585">
-        <v>0</v>
-      </c>
+      <c r="N585"/>
       <c r="O585" t="s">
         <v>1217</v>
       </c>
@@ -34372,9 +33198,7 @@
       <c r="M586">
         <v>13</v>
       </c>
-      <c r="N586">
-        <v>0</v>
-      </c>
+      <c r="N586"/>
       <c r="O586" t="s">
         <v>1220</v>
       </c>
@@ -34422,9 +33246,7 @@
       <c r="M587">
         <v>3</v>
       </c>
-      <c r="N587">
-        <v>0</v>
-      </c>
+      <c r="N587"/>
       <c r="O587" t="s">
         <v>1223</v>
       </c>
@@ -34472,9 +33294,7 @@
       <c r="M588">
         <v>16</v>
       </c>
-      <c r="N588">
-        <v>0</v>
-      </c>
+      <c r="N588"/>
       <c r="O588" t="s">
         <v>1227</v>
       </c>
@@ -34522,9 +33342,7 @@
       <c r="M589">
         <v>14</v>
       </c>
-      <c r="N589">
-        <v>0</v>
-      </c>
+      <c r="N589"/>
       <c r="O589" t="s">
         <v>1228</v>
       </c>
@@ -34572,9 +33390,7 @@
       <c r="M590">
         <v>10</v>
       </c>
-      <c r="N590">
-        <v>0</v>
-      </c>
+      <c r="N590"/>
       <c r="O590" t="s">
         <v>1229</v>
       </c>
@@ -34622,9 +33438,7 @@
       <c r="M591">
         <v>11</v>
       </c>
-      <c r="N591">
-        <v>0</v>
-      </c>
+      <c r="N591"/>
       <c r="O591" t="s">
         <v>1230</v>
       </c>
@@ -34672,9 +33486,7 @@
       <c r="M592">
         <v>15</v>
       </c>
-      <c r="N592">
-        <v>0</v>
-      </c>
+      <c r="N592"/>
       <c r="O592" t="s">
         <v>1232</v>
       </c>
@@ -34722,9 +33534,7 @@
       <c r="M593">
         <v>5</v>
       </c>
-      <c r="N593">
-        <v>0</v>
-      </c>
+      <c r="N593"/>
       <c r="O593" t="s">
         <v>1234</v>
       </c>
@@ -34772,9 +33582,7 @@
       <c r="M594">
         <v>4</v>
       </c>
-      <c r="N594">
-        <v>0</v>
-      </c>
+      <c r="N594"/>
       <c r="O594" t="s">
         <v>1236</v>
       </c>
@@ -34822,9 +33630,7 @@
       <c r="M595">
         <v>12</v>
       </c>
-      <c r="N595">
-        <v>0</v>
-      </c>
+      <c r="N595"/>
       <c r="O595" t="s">
         <v>1238</v>
       </c>
@@ -34872,9 +33678,7 @@
       <c r="M596">
         <v>6</v>
       </c>
-      <c r="N596">
-        <v>0</v>
-      </c>
+      <c r="N596"/>
       <c r="O596" t="s">
         <v>1240</v>
       </c>
@@ -34922,9 +33726,7 @@
       <c r="M597">
         <v>6</v>
       </c>
-      <c r="N597">
-        <v>0</v>
-      </c>
+      <c r="N597"/>
       <c r="O597" t="s">
         <v>1241</v>
       </c>
@@ -34972,9 +33774,7 @@
       <c r="M598">
         <v>4</v>
       </c>
-      <c r="N598">
-        <v>0</v>
-      </c>
+      <c r="N598"/>
       <c r="O598" t="s">
         <v>1243</v>
       </c>
@@ -35022,9 +33822,7 @@
       <c r="M599">
         <v>5</v>
       </c>
-      <c r="N599">
-        <v>0</v>
-      </c>
+      <c r="N599"/>
       <c r="O599" t="s">
         <v>1244</v>
       </c>
@@ -35072,9 +33870,7 @@
       <c r="M600">
         <v>6</v>
       </c>
-      <c r="N600">
-        <v>0</v>
-      </c>
+      <c r="N600"/>
       <c r="O600" t="s">
         <v>1246</v>
       </c>
@@ -35122,9 +33918,7 @@
       <c r="M601">
         <v>5</v>
       </c>
-      <c r="N601">
-        <v>0</v>
-      </c>
+      <c r="N601"/>
       <c r="O601" t="s">
         <v>1248</v>
       </c>
@@ -35172,9 +33966,7 @@
       <c r="M602">
         <v>8</v>
       </c>
-      <c r="N602">
-        <v>0</v>
-      </c>
+      <c r="N602"/>
       <c r="O602" t="s">
         <v>1250</v>
       </c>
@@ -35222,9 +34014,7 @@
       <c r="M603">
         <v>7</v>
       </c>
-      <c r="N603">
-        <v>0</v>
-      </c>
+      <c r="N603"/>
       <c r="O603" t="s">
         <v>1251</v>
       </c>
@@ -35272,9 +34062,7 @@
       <c r="M604">
         <v>4</v>
       </c>
-      <c r="N604">
-        <v>0</v>
-      </c>
+      <c r="N604"/>
       <c r="O604" t="s">
         <v>1253</v>
       </c>
@@ -35322,9 +34110,7 @@
       <c r="M605">
         <v>4</v>
       </c>
-      <c r="N605">
-        <v>0</v>
-      </c>
+      <c r="N605"/>
       <c r="O605" t="s">
         <v>1254</v>
       </c>
@@ -35372,9 +34158,7 @@
       <c r="M606">
         <v>4</v>
       </c>
-      <c r="N606">
-        <v>0</v>
-      </c>
+      <c r="N606"/>
       <c r="O606" t="s">
         <v>1255</v>
       </c>
@@ -35422,9 +34206,7 @@
       <c r="M607">
         <v>4</v>
       </c>
-      <c r="N607">
-        <v>0</v>
-      </c>
+      <c r="N607"/>
       <c r="O607" t="s">
         <v>1256</v>
       </c>
@@ -35472,9 +34254,7 @@
       <c r="M608">
         <v>5</v>
       </c>
-      <c r="N608">
-        <v>0</v>
-      </c>
+      <c r="N608"/>
       <c r="O608" t="s">
         <v>1257</v>
       </c>
@@ -35522,9 +34302,7 @@
       <c r="M609">
         <v>4</v>
       </c>
-      <c r="N609">
-        <v>0</v>
-      </c>
+      <c r="N609"/>
       <c r="O609" t="s">
         <v>1258</v>
       </c>
@@ -35572,9 +34350,7 @@
       <c r="M610">
         <v>1</v>
       </c>
-      <c r="N610">
-        <v>0</v>
-      </c>
+      <c r="N610"/>
       <c r="O610" t="s">
         <v>1259</v>
       </c>
@@ -35622,9 +34398,7 @@
       <c r="M611">
         <v>35</v>
       </c>
-      <c r="N611">
-        <v>0</v>
-      </c>
+      <c r="N611"/>
       <c r="O611" t="s">
         <v>1262</v>
       </c>
@@ -35672,9 +34446,7 @@
       <c r="M612">
         <v>1</v>
       </c>
-      <c r="N612">
-        <v>0</v>
-      </c>
+      <c r="N612"/>
       <c r="O612" t="s">
         <v>1263</v>
       </c>
@@ -35722,9 +34494,7 @@
       <c r="M613">
         <v>11</v>
       </c>
-      <c r="N613">
-        <v>0</v>
-      </c>
+      <c r="N613"/>
       <c r="O613" t="s">
         <v>1265</v>
       </c>
@@ -35772,9 +34542,7 @@
       <c r="M614">
         <v>4</v>
       </c>
-      <c r="N614">
-        <v>0</v>
-      </c>
+      <c r="N614"/>
       <c r="O614" t="s">
         <v>1266</v>
       </c>
@@ -35822,9 +34590,7 @@
       <c r="M615">
         <v>1</v>
       </c>
-      <c r="N615">
-        <v>0</v>
-      </c>
+      <c r="N615"/>
       <c r="O615" t="s">
         <v>1268</v>
       </c>
@@ -35872,9 +34638,7 @@
       <c r="M616">
         <v>2</v>
       </c>
-      <c r="N616">
-        <v>0</v>
-      </c>
+      <c r="N616"/>
       <c r="O616" t="s">
         <v>1269</v>
       </c>
@@ -35922,9 +34686,7 @@
       <c r="M617">
         <v>5</v>
       </c>
-      <c r="N617">
-        <v>0</v>
-      </c>
+      <c r="N617"/>
       <c r="O617" t="s">
         <v>1270</v>
       </c>
@@ -35972,9 +34734,7 @@
       <c r="M618">
         <v>1</v>
       </c>
-      <c r="N618">
-        <v>0</v>
-      </c>
+      <c r="N618"/>
       <c r="O618" t="s">
         <v>1271</v>
       </c>
@@ -36022,9 +34782,7 @@
       <c r="M619">
         <v>1</v>
       </c>
-      <c r="N619">
-        <v>0</v>
-      </c>
+      <c r="N619"/>
       <c r="O619" t="s">
         <v>1272</v>
       </c>
@@ -36072,9 +34830,7 @@
       <c r="M620">
         <v>15</v>
       </c>
-      <c r="N620">
-        <v>0</v>
-      </c>
+      <c r="N620"/>
       <c r="O620" t="s">
         <v>1273</v>
       </c>
@@ -36122,9 +34878,7 @@
       <c r="M621">
         <v>1</v>
       </c>
-      <c r="N621">
-        <v>0</v>
-      </c>
+      <c r="N621"/>
       <c r="O621" t="s">
         <v>1274</v>
       </c>
@@ -36172,9 +34926,7 @@
       <c r="M622">
         <v>1</v>
       </c>
-      <c r="N622">
-        <v>0</v>
-      </c>
+      <c r="N622"/>
       <c r="O622" t="s">
         <v>1275</v>
       </c>
@@ -36222,9 +34974,7 @@
       <c r="M623">
         <v>11</v>
       </c>
-      <c r="N623">
-        <v>0</v>
-      </c>
+      <c r="N623"/>
       <c r="O623" t="s">
         <v>1277</v>
       </c>
@@ -36272,9 +35022,7 @@
       <c r="M624">
         <v>1</v>
       </c>
-      <c r="N624">
-        <v>0</v>
-      </c>
+      <c r="N624"/>
       <c r="O624" t="s">
         <v>1278</v>
       </c>
@@ -36322,9 +35070,7 @@
       <c r="M625">
         <v>1</v>
       </c>
-      <c r="N625">
-        <v>0</v>
-      </c>
+      <c r="N625"/>
       <c r="O625" t="s">
         <v>1279</v>
       </c>
@@ -36372,9 +35118,7 @@
       <c r="M626">
         <v>1</v>
       </c>
-      <c r="N626">
-        <v>0</v>
-      </c>
+      <c r="N626"/>
       <c r="O626" t="s">
         <v>1280</v>
       </c>
@@ -36422,9 +35166,7 @@
       <c r="M627">
         <v>4</v>
       </c>
-      <c r="N627">
-        <v>0</v>
-      </c>
+      <c r="N627"/>
       <c r="O627" t="s">
         <v>1282</v>
       </c>
@@ -36472,9 +35214,7 @@
       <c r="M628">
         <v>10</v>
       </c>
-      <c r="N628">
-        <v>0</v>
-      </c>
+      <c r="N628"/>
       <c r="O628" t="s">
         <v>1284</v>
       </c>
@@ -36522,9 +35262,7 @@
       <c r="M629">
         <v>8</v>
       </c>
-      <c r="N629">
-        <v>0</v>
-      </c>
+      <c r="N629"/>
       <c r="O629" t="s">
         <v>1285</v>
       </c>
@@ -36572,9 +35310,7 @@
       <c r="M630">
         <v>6</v>
       </c>
-      <c r="N630">
-        <v>0</v>
-      </c>
+      <c r="N630"/>
       <c r="O630" t="s">
         <v>1287</v>
       </c>
@@ -36622,9 +35358,7 @@
       <c r="M631">
         <v>1</v>
       </c>
-      <c r="N631">
-        <v>0</v>
-      </c>
+      <c r="N631"/>
       <c r="O631" t="s">
         <v>1288</v>
       </c>
@@ -36672,9 +35406,7 @@
       <c r="M632">
         <v>1</v>
       </c>
-      <c r="N632">
-        <v>0</v>
-      </c>
+      <c r="N632"/>
       <c r="O632" t="s">
         <v>1290</v>
       </c>
@@ -36722,9 +35454,7 @@
       <c r="M633">
         <v>2</v>
       </c>
-      <c r="N633">
-        <v>0</v>
-      </c>
+      <c r="N633"/>
       <c r="O633" t="s">
         <v>1291</v>
       </c>
@@ -36772,9 +35502,7 @@
       <c r="M634">
         <v>2</v>
       </c>
-      <c r="N634">
-        <v>0</v>
-      </c>
+      <c r="N634"/>
       <c r="O634" t="s">
         <v>1292</v>
       </c>
@@ -36822,9 +35550,7 @@
       <c r="M635">
         <v>2</v>
       </c>
-      <c r="N635">
-        <v>0</v>
-      </c>
+      <c r="N635"/>
       <c r="O635" t="s">
         <v>1293</v>
       </c>
@@ -36872,9 +35598,7 @@
       <c r="M636">
         <v>3</v>
       </c>
-      <c r="N636">
-        <v>0</v>
-      </c>
+      <c r="N636"/>
       <c r="O636" t="s">
         <v>1294</v>
       </c>
@@ -36922,9 +35646,7 @@
       <c r="M637">
         <v>3</v>
       </c>
-      <c r="N637">
-        <v>0</v>
-      </c>
+      <c r="N637"/>
       <c r="O637" t="s">
         <v>1296</v>
       </c>
@@ -36972,9 +35694,7 @@
       <c r="M638">
         <v>3</v>
       </c>
-      <c r="N638">
-        <v>0</v>
-      </c>
+      <c r="N638"/>
       <c r="O638" t="s">
         <v>1298</v>
       </c>
@@ -37022,9 +35742,7 @@
       <c r="M639">
         <v>22</v>
       </c>
-      <c r="N639">
-        <v>0</v>
-      </c>
+      <c r="N639"/>
       <c r="O639" t="s">
         <v>1300</v>
       </c>
@@ -37072,9 +35790,7 @@
       <c r="M640">
         <v>4</v>
       </c>
-      <c r="N640">
-        <v>0</v>
-      </c>
+      <c r="N640"/>
       <c r="O640" t="s">
         <v>1302</v>
       </c>
@@ -37122,9 +35838,7 @@
       <c r="M641">
         <v>1</v>
       </c>
-      <c r="N641">
-        <v>0</v>
-      </c>
+      <c r="N641"/>
       <c r="O641" t="s">
         <v>1304</v>
       </c>
@@ -37172,9 +35886,7 @@
       <c r="M642">
         <v>5</v>
       </c>
-      <c r="N642">
-        <v>0</v>
-      </c>
+      <c r="N642"/>
       <c r="O642" t="s">
         <v>1305</v>
       </c>
@@ -37222,9 +35934,7 @@
       <c r="M643">
         <v>1</v>
       </c>
-      <c r="N643">
-        <v>0</v>
-      </c>
+      <c r="N643"/>
       <c r="O643" t="s">
         <v>1306</v>
       </c>
@@ -37272,9 +35982,7 @@
       <c r="M644">
         <v>8</v>
       </c>
-      <c r="N644">
-        <v>0</v>
-      </c>
+      <c r="N644"/>
       <c r="O644" t="s">
         <v>1308</v>
       </c>
@@ -37322,9 +36030,7 @@
       <c r="M645">
         <v>8</v>
       </c>
-      <c r="N645">
-        <v>0</v>
-      </c>
+      <c r="N645"/>
       <c r="O645" t="s">
         <v>1310</v>
       </c>
@@ -37372,9 +36078,7 @@
       <c r="M646">
         <v>9</v>
       </c>
-      <c r="N646">
-        <v>0</v>
-      </c>
+      <c r="N646"/>
       <c r="O646" t="s">
         <v>1312</v>
       </c>
@@ -37422,9 +36126,7 @@
       <c r="M647">
         <v>217</v>
       </c>
-      <c r="N647">
-        <v>0</v>
-      </c>
+      <c r="N647"/>
       <c r="O647" t="s">
         <v>1315</v>
       </c>
@@ -37472,9 +36174,7 @@
       <c r="M648">
         <v>55</v>
       </c>
-      <c r="N648">
-        <v>0</v>
-      </c>
+      <c r="N648"/>
       <c r="O648" t="s">
         <v>1317</v>
       </c>
@@ -37522,9 +36222,7 @@
       <c r="M649">
         <v>56</v>
       </c>
-      <c r="N649">
-        <v>0</v>
-      </c>
+      <c r="N649"/>
       <c r="O649" t="s">
         <v>1319</v>
       </c>
@@ -37572,9 +36270,7 @@
       <c r="M650">
         <v>55</v>
       </c>
-      <c r="N650">
-        <v>0</v>
-      </c>
+      <c r="N650"/>
       <c r="O650" t="s">
         <v>1321</v>
       </c>
@@ -37622,9 +36318,7 @@
       <c r="M651">
         <v>46</v>
       </c>
-      <c r="N651">
-        <v>0</v>
-      </c>
+      <c r="N651"/>
       <c r="O651" t="s">
         <v>1323</v>
       </c>
@@ -37672,9 +36366,7 @@
       <c r="M652">
         <v>46</v>
       </c>
-      <c r="N652">
-        <v>0</v>
-      </c>
+      <c r="N652"/>
       <c r="O652" t="s">
         <v>1325</v>
       </c>
@@ -37722,9 +36414,7 @@
       <c r="M653">
         <v>72</v>
       </c>
-      <c r="N653">
-        <v>0</v>
-      </c>
+      <c r="N653"/>
       <c r="O653" t="s">
         <v>1327</v>
       </c>
@@ -37772,9 +36462,7 @@
       <c r="M654">
         <v>36</v>
       </c>
-      <c r="N654">
-        <v>0</v>
-      </c>
+      <c r="N654"/>
       <c r="O654" t="s">
         <v>1329</v>
       </c>
@@ -37822,9 +36510,7 @@
       <c r="M655">
         <v>66</v>
       </c>
-      <c r="N655">
-        <v>0</v>
-      </c>
+      <c r="N655"/>
       <c r="O655" t="s">
         <v>1331</v>
       </c>
@@ -37872,9 +36558,7 @@
       <c r="M656">
         <v>47</v>
       </c>
-      <c r="N656">
-        <v>0</v>
-      </c>
+      <c r="N656"/>
       <c r="O656" t="s">
         <v>1333</v>
       </c>
@@ -37922,9 +36606,7 @@
       <c r="M657">
         <v>73</v>
       </c>
-      <c r="N657">
-        <v>0</v>
-      </c>
+      <c r="N657"/>
       <c r="O657" t="s">
         <v>1335</v>
       </c>
@@ -37972,9 +36654,7 @@
       <c r="M658">
         <v>41</v>
       </c>
-      <c r="N658">
-        <v>0</v>
-      </c>
+      <c r="N658"/>
       <c r="O658" t="s">
         <v>1337</v>
       </c>
@@ -38022,9 +36702,7 @@
       <c r="M659">
         <v>39</v>
       </c>
-      <c r="N659">
-        <v>0</v>
-      </c>
+      <c r="N659"/>
       <c r="O659" t="s">
         <v>1340</v>
       </c>
@@ -38072,9 +36750,7 @@
       <c r="M660">
         <v>43</v>
       </c>
-      <c r="N660">
-        <v>0</v>
-      </c>
+      <c r="N660"/>
       <c r="O660" t="s">
         <v>1342</v>
       </c>
@@ -38122,9 +36798,7 @@
       <c r="M661">
         <v>40</v>
       </c>
-      <c r="N661">
-        <v>0</v>
-      </c>
+      <c r="N661"/>
       <c r="O661" t="s">
         <v>1347</v>
       </c>
@@ -38172,9 +36846,7 @@
       <c r="M662">
         <v>83</v>
       </c>
-      <c r="N662">
-        <v>0</v>
-      </c>
+      <c r="N662"/>
       <c r="O662" t="s">
         <v>1350</v>
       </c>
@@ -38222,9 +36894,7 @@
       <c r="M663">
         <v>79</v>
       </c>
-      <c r="N663">
-        <v>0</v>
-      </c>
+      <c r="N663"/>
       <c r="O663" t="s">
         <v>1352</v>
       </c>
@@ -38233,6 +36903,9 @@
       </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink ref="O6" r:id="rId1" display="http://data.huangshi.gov.cn/myapi/Datainfo/view?infoid=683"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <headerFooter/>
 </worksheet>
